--- a/templates/request_equipment_template.xlsx
+++ b/templates/request_equipment_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{536CD768-408E-4B4C-BE40-CCAAA6665A92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{374ED829-485F-47EA-ACB9-CD0647D87317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E0EBB611-D57A-40BF-92BA-E23262599980}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>Termo de Requisição de Material</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>O Receptor</t>
-  </si>
-  <si>
-    <t>12346579-6547</t>
   </si>
 </sst>
 </file>
@@ -407,14 +404,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>287249</xdr:colOff>
+      <xdr:colOff>406400</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>86026</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Imagem 1">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C4A2692-659C-4420-8C80-6E12E97DDC65}"/>
@@ -426,7 +422,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -440,7 +436,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="104774" y="104776"/>
-          <a:ext cx="3230475" cy="648000"/>
+          <a:ext cx="2593976" cy="648000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -458,7 +454,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>196850</xdr:colOff>
+      <xdr:colOff>146050</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>3175</xdr:rowOff>
     </xdr:to>
@@ -476,7 +472,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -489,7 +485,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="107950" y="8453755"/>
+          <a:off x="107950" y="8504555"/>
           <a:ext cx="3194050" cy="96520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -502,22 +498,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>234950</xdr:colOff>
+      <xdr:colOff>260350</xdr:colOff>
       <xdr:row>47</xdr:row>
       <xdr:rowOff>128905</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>463550</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
       <xdr:row>48</xdr:row>
       <xdr:rowOff>3175</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Imagem 7">
+        <xdr:cNvPr id="9" name="Imagem 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC84C4FC-8B29-4C69-BC75-C7FB6F2C2EE5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C429B18-5BE9-4555-88A4-B56F3024BF20}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -526,7 +522,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -539,7 +535,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2571750" y="8453755"/>
+          <a:off x="2552700" y="8504555"/>
           <a:ext cx="3194050" cy="96520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -874,7 +870,7 @@
   <cols>
     <col min="1" max="1" width="1.42578125" customWidth="1"/>
     <col min="2" max="2" width="8.5703125" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" customWidth="1"/>
     <col min="4" max="4" width="8.5703125" customWidth="1"/>
     <col min="5" max="5" width="1.42578125" customWidth="1"/>
     <col min="6" max="10" width="6.42578125" customWidth="1"/>
@@ -956,13 +952,13 @@
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="4"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
-      <c r="K16" s="5"/>
-      <c r="L16" s="5"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
       <c r="M16" s="3" t="s">
         <v>2</v>
       </c>
@@ -984,9 +980,7 @@
       <c r="N17" s="3"/>
     </row>
     <row r="18" spans="2:14" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="B18" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="B18" s="5"/>
       <c r="C18" s="5"/>
       <c r="D18" s="7" t="s">
         <v>3</v>

--- a/templates/request_equipment_template.xlsx
+++ b/templates/request_equipment_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37436A12-1697-4D22-A989-767639EE6260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B069E8B-BA22-4A41-864C-3E6458CDD737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4331DD6E-67AF-48F9-ABB9-6D96E0057117}"/>
   </bookViews>
@@ -84,16 +84,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -228,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -246,12 +238,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -261,22 +247,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -291,6 +283,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -780,153 +784,153 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC5CA20A-A8C5-4159-992A-54296072ECF2}">
-  <dimension ref="B8:BQ55"/>
+  <dimension ref="B8:BR55"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="55" width="1.28515625" customWidth="1"/>
-    <col min="56" max="65" width="1.140625" customWidth="1"/>
-    <col min="66" max="69" width="1.28515625" customWidth="1"/>
+    <col min="56" max="64" width="1.140625" customWidth="1"/>
+    <col min="65" max="69" width="1.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="8" spans="2:69" x14ac:dyDescent="0.25">
-      <c r="B8" s="19" t="s">
+    <row r="8" spans="2:69" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B8" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
-      <c r="Q8" s="19"/>
-      <c r="R8" s="19"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
-      <c r="U8" s="19"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="19"/>
-      <c r="X8" s="19"/>
-      <c r="Y8" s="19"/>
-      <c r="Z8" s="19"/>
-      <c r="AA8" s="19"/>
-      <c r="AB8" s="19"/>
-      <c r="AC8" s="19"/>
-      <c r="AD8" s="19"/>
-      <c r="AE8" s="19"/>
-      <c r="AF8" s="19"/>
-      <c r="AG8" s="19"/>
-      <c r="AH8" s="19"/>
-      <c r="AI8" s="19"/>
-      <c r="AJ8" s="19"/>
-      <c r="AK8" s="19"/>
-      <c r="AL8" s="19"/>
-      <c r="AM8" s="19"/>
-      <c r="AN8" s="19"/>
-      <c r="AO8" s="19"/>
-      <c r="AP8" s="19"/>
-      <c r="AQ8" s="19"/>
-      <c r="AR8" s="19"/>
-      <c r="AS8" s="19"/>
-      <c r="AT8" s="19"/>
-      <c r="AU8" s="19"/>
-      <c r="AV8" s="19"/>
-      <c r="AW8" s="19"/>
-      <c r="AX8" s="19"/>
-      <c r="AY8" s="19"/>
-      <c r="AZ8" s="19"/>
-      <c r="BA8" s="19"/>
-      <c r="BB8" s="19"/>
-      <c r="BC8" s="19"/>
-      <c r="BD8" s="19"/>
-      <c r="BE8" s="19"/>
-      <c r="BF8" s="19"/>
-      <c r="BG8" s="19"/>
-      <c r="BH8" s="19"/>
-      <c r="BI8" s="19"/>
-      <c r="BJ8" s="19"/>
-      <c r="BK8" s="19"/>
-      <c r="BL8" s="19"/>
-      <c r="BM8" s="19"/>
-      <c r="BN8" s="19"/>
-      <c r="BO8" s="19"/>
-      <c r="BP8" s="19"/>
-    </row>
-    <row r="9" spans="2:69" x14ac:dyDescent="0.25">
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19"/>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
-      <c r="T9" s="19"/>
-      <c r="U9" s="19"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="19"/>
-      <c r="X9" s="19"/>
-      <c r="Y9" s="19"/>
-      <c r="Z9" s="19"/>
-      <c r="AA9" s="19"/>
-      <c r="AB9" s="19"/>
-      <c r="AC9" s="19"/>
-      <c r="AD9" s="19"/>
-      <c r="AE9" s="19"/>
-      <c r="AF9" s="19"/>
-      <c r="AG9" s="19"/>
-      <c r="AH9" s="19"/>
-      <c r="AI9" s="19"/>
-      <c r="AJ9" s="19"/>
-      <c r="AK9" s="19"/>
-      <c r="AL9" s="19"/>
-      <c r="AM9" s="19"/>
-      <c r="AN9" s="19"/>
-      <c r="AO9" s="19"/>
-      <c r="AP9" s="19"/>
-      <c r="AQ9" s="19"/>
-      <c r="AR9" s="19"/>
-      <c r="AS9" s="19"/>
-      <c r="AT9" s="19"/>
-      <c r="AU9" s="19"/>
-      <c r="AV9" s="19"/>
-      <c r="AW9" s="19"/>
-      <c r="AX9" s="19"/>
-      <c r="AY9" s="19"/>
-      <c r="AZ9" s="19"/>
-      <c r="BA9" s="19"/>
-      <c r="BB9" s="19"/>
-      <c r="BC9" s="19"/>
-      <c r="BD9" s="19"/>
-      <c r="BE9" s="19"/>
-      <c r="BF9" s="19"/>
-      <c r="BG9" s="19"/>
-      <c r="BH9" s="19"/>
-      <c r="BI9" s="19"/>
-      <c r="BJ9" s="19"/>
-      <c r="BK9" s="19"/>
-      <c r="BL9" s="19"/>
-      <c r="BM9" s="19"/>
-      <c r="BN9" s="19"/>
-      <c r="BO9" s="19"/>
-      <c r="BP9" s="19"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17"/>
+      <c r="S8" s="17"/>
+      <c r="T8" s="17"/>
+      <c r="U8" s="17"/>
+      <c r="V8" s="17"/>
+      <c r="W8" s="17"/>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="17"/>
+      <c r="AA8" s="17"/>
+      <c r="AB8" s="17"/>
+      <c r="AC8" s="17"/>
+      <c r="AD8" s="17"/>
+      <c r="AE8" s="17"/>
+      <c r="AF8" s="17"/>
+      <c r="AG8" s="17"/>
+      <c r="AH8" s="17"/>
+      <c r="AI8" s="17"/>
+      <c r="AJ8" s="17"/>
+      <c r="AK8" s="17"/>
+      <c r="AL8" s="17"/>
+      <c r="AM8" s="17"/>
+      <c r="AN8" s="17"/>
+      <c r="AO8" s="17"/>
+      <c r="AP8" s="17"/>
+      <c r="AQ8" s="17"/>
+      <c r="AR8" s="17"/>
+      <c r="AS8" s="17"/>
+      <c r="AT8" s="17"/>
+      <c r="AU8" s="17"/>
+      <c r="AV8" s="17"/>
+      <c r="AW8" s="17"/>
+      <c r="AX8" s="17"/>
+      <c r="AY8" s="17"/>
+      <c r="AZ8" s="17"/>
+      <c r="BA8" s="17"/>
+      <c r="BB8" s="17"/>
+      <c r="BC8" s="17"/>
+      <c r="BD8" s="17"/>
+      <c r="BE8" s="17"/>
+      <c r="BF8" s="17"/>
+      <c r="BG8" s="17"/>
+      <c r="BH8" s="17"/>
+      <c r="BI8" s="17"/>
+      <c r="BJ8" s="17"/>
+      <c r="BK8" s="17"/>
+      <c r="BL8" s="17"/>
+      <c r="BM8" s="17"/>
+      <c r="BN8" s="17"/>
+      <c r="BO8" s="17"/>
+      <c r="BP8" s="31"/>
+    </row>
+    <row r="9" spans="2:69" ht="19.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="Q9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="17"/>
+      <c r="Y9" s="17"/>
+      <c r="Z9" s="17"/>
+      <c r="AA9" s="17"/>
+      <c r="AB9" s="17"/>
+      <c r="AC9" s="17"/>
+      <c r="AD9" s="17"/>
+      <c r="AE9" s="17"/>
+      <c r="AF9" s="17"/>
+      <c r="AG9" s="17"/>
+      <c r="AH9" s="17"/>
+      <c r="AI9" s="17"/>
+      <c r="AJ9" s="17"/>
+      <c r="AK9" s="17"/>
+      <c r="AL9" s="17"/>
+      <c r="AM9" s="17"/>
+      <c r="AN9" s="17"/>
+      <c r="AO9" s="17"/>
+      <c r="AP9" s="17"/>
+      <c r="AQ9" s="17"/>
+      <c r="AR9" s="17"/>
+      <c r="AS9" s="17"/>
+      <c r="AT9" s="17"/>
+      <c r="AU9" s="17"/>
+      <c r="AV9" s="17"/>
+      <c r="AW9" s="17"/>
+      <c r="AX9" s="17"/>
+      <c r="AY9" s="17"/>
+      <c r="AZ9" s="17"/>
+      <c r="BA9" s="17"/>
+      <c r="BB9" s="17"/>
+      <c r="BC9" s="17"/>
+      <c r="BD9" s="17"/>
+      <c r="BE9" s="17"/>
+      <c r="BF9" s="17"/>
+      <c r="BG9" s="17"/>
+      <c r="BH9" s="17"/>
+      <c r="BI9" s="17"/>
+      <c r="BJ9" s="17"/>
+      <c r="BK9" s="17"/>
+      <c r="BL9" s="17"/>
+      <c r="BM9" s="17"/>
+      <c r="BN9" s="17"/>
+      <c r="BO9" s="17"/>
+      <c r="BP9" s="31"/>
     </row>
     <row r="12" spans="2:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
@@ -951,47 +955,47 @@
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
-      <c r="V12" s="8"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="8"/>
-      <c r="Z12" s="8"/>
-      <c r="AA12" s="8"/>
-      <c r="AB12" s="8"/>
-      <c r="AC12" s="8"/>
-      <c r="AD12" s="8"/>
-      <c r="AE12" s="8"/>
-      <c r="AF12" s="8"/>
-      <c r="AG12" s="8"/>
-      <c r="AH12" s="8"/>
-      <c r="AI12" s="8"/>
-      <c r="AJ12" s="8"/>
-      <c r="AK12" s="8"/>
-      <c r="AL12" s="8"/>
-      <c r="AM12" s="8"/>
-      <c r="AN12" s="8"/>
-      <c r="AO12" s="8"/>
-      <c r="AP12" s="8"/>
-      <c r="AQ12" s="8"/>
-      <c r="AR12" s="8"/>
-      <c r="AS12" s="8"/>
-      <c r="AT12" s="8"/>
-      <c r="AU12" s="8"/>
-      <c r="AV12" s="8"/>
-      <c r="AW12" s="8"/>
-      <c r="AX12" s="8"/>
-      <c r="AY12" s="8"/>
-      <c r="AZ12" s="8"/>
-      <c r="BA12" s="8"/>
-      <c r="BB12" s="8"/>
-      <c r="BC12" s="8"/>
-      <c r="BD12" s="8"/>
-      <c r="BE12" s="8"/>
-      <c r="BF12" s="8"/>
-      <c r="BG12" s="8"/>
-      <c r="BH12" s="3" t="s">
+      <c r="V12" s="30"/>
+      <c r="W12" s="30"/>
+      <c r="X12" s="30"/>
+      <c r="Y12" s="30"/>
+      <c r="Z12" s="30"/>
+      <c r="AA12" s="30"/>
+      <c r="AB12" s="30"/>
+      <c r="AC12" s="30"/>
+      <c r="AD12" s="30"/>
+      <c r="AE12" s="30"/>
+      <c r="AF12" s="30"/>
+      <c r="AG12" s="30"/>
+      <c r="AH12" s="30"/>
+      <c r="AI12" s="30"/>
+      <c r="AJ12" s="30"/>
+      <c r="AK12" s="30"/>
+      <c r="AL12" s="30"/>
+      <c r="AM12" s="30"/>
+      <c r="AN12" s="30"/>
+      <c r="AO12" s="30"/>
+      <c r="AP12" s="30"/>
+      <c r="AQ12" s="30"/>
+      <c r="AR12" s="30"/>
+      <c r="AS12" s="30"/>
+      <c r="AT12" s="30"/>
+      <c r="AU12" s="30"/>
+      <c r="AV12" s="30"/>
+      <c r="AW12" s="30"/>
+      <c r="AX12" s="30"/>
+      <c r="AY12" s="30"/>
+      <c r="AZ12" s="30"/>
+      <c r="BA12" s="30"/>
+      <c r="BB12" s="30"/>
+      <c r="BC12" s="30"/>
+      <c r="BD12" s="30"/>
+      <c r="BE12" s="30"/>
+      <c r="BF12" s="30"/>
+      <c r="BG12" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="BH12" s="3"/>
       <c r="BI12" s="3"/>
       <c r="BJ12" s="3"/>
       <c r="BK12" s="3"/>
@@ -1060,7 +1064,7 @@
       <c r="BD13" s="4"/>
       <c r="BE13" s="4"/>
       <c r="BF13" s="4"/>
-      <c r="BG13" s="4"/>
+      <c r="BG13" s="5"/>
       <c r="BH13" s="5"/>
       <c r="BI13" s="5"/>
       <c r="BJ13" s="5"/>
@@ -1073,45 +1077,45 @@
       <c r="BQ13" s="5"/>
     </row>
     <row r="14" spans="2:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="3" t="s">
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
-      <c r="S14" s="3"/>
-      <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="7"/>
-      <c r="Z14" s="7"/>
-      <c r="AA14" s="7"/>
-      <c r="AB14" s="7"/>
-      <c r="AC14" s="7"/>
-      <c r="AD14" s="7"/>
-      <c r="AE14" s="7"/>
-      <c r="AF14" s="7"/>
-      <c r="AG14" s="7"/>
-      <c r="AH14" s="7"/>
-      <c r="AI14" s="7"/>
-      <c r="AJ14" s="7"/>
-      <c r="AK14" s="7"/>
-      <c r="AL14" s="7"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
+      <c r="Z14" s="23"/>
+      <c r="AA14" s="23"/>
+      <c r="AB14" s="23"/>
+      <c r="AC14" s="23"/>
+      <c r="AD14" s="23"/>
+      <c r="AE14" s="23"/>
+      <c r="AF14" s="23"/>
+      <c r="AG14" s="23"/>
+      <c r="AH14" s="23"/>
+      <c r="AI14" s="23"/>
+      <c r="AJ14" s="23"/>
+      <c r="AK14" s="23"/>
+      <c r="AL14" s="23"/>
       <c r="AM14" s="5" t="s">
         <v>3</v>
       </c>
@@ -1138,7 +1142,7 @@
       <c r="BH14" s="5"/>
       <c r="BI14" s="5"/>
       <c r="BJ14" s="5"/>
-      <c r="BK14" s="5"/>
+      <c r="BK14" s="6"/>
       <c r="BL14" s="6"/>
       <c r="BM14" s="6"/>
       <c r="BN14" s="6"/>
@@ -1359,73 +1363,73 @@
       <c r="BQ17" s="6"/>
     </row>
     <row r="18" spans="2:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="8"/>
-      <c r="Z18" s="8"/>
-      <c r="AA18" s="8"/>
-      <c r="AB18" s="8"/>
-      <c r="AC18" s="8"/>
-      <c r="AD18" s="8"/>
-      <c r="AE18" s="8"/>
-      <c r="AF18" s="8"/>
-      <c r="AG18" s="8"/>
-      <c r="AH18" s="8"/>
-      <c r="AI18" s="8"/>
-      <c r="AJ18" s="8"/>
-      <c r="AK18" s="8"/>
-      <c r="AL18" s="8"/>
-      <c r="AM18" s="8"/>
-      <c r="AN18" s="8"/>
-      <c r="AO18" s="8"/>
-      <c r="AP18" s="8"/>
-      <c r="AQ18" s="8"/>
-      <c r="AR18" s="8"/>
-      <c r="AS18" s="8"/>
-      <c r="AT18" s="8"/>
-      <c r="AU18" s="8"/>
-      <c r="AV18" s="8"/>
-      <c r="AW18" s="8"/>
-      <c r="AX18" s="8"/>
-      <c r="AY18" s="8"/>
-      <c r="AZ18" s="8"/>
-      <c r="BA18" s="8"/>
-      <c r="BB18" s="8"/>
-      <c r="BC18" s="8"/>
-      <c r="BD18" s="8"/>
-      <c r="BE18" s="8"/>
-      <c r="BF18" s="8"/>
-      <c r="BG18" s="8"/>
-      <c r="BH18" s="8"/>
-      <c r="BI18" s="8"/>
-      <c r="BJ18" s="8"/>
-      <c r="BK18" s="8"/>
-      <c r="BL18" s="8"/>
-      <c r="BM18" s="8"/>
-      <c r="BN18" s="8"/>
-      <c r="BO18" s="8"/>
-      <c r="BP18" s="8"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="30"/>
+      <c r="L18" s="30"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="30"/>
+      <c r="O18" s="30"/>
+      <c r="P18" s="30"/>
+      <c r="Q18" s="30"/>
+      <c r="R18" s="30"/>
+      <c r="S18" s="30"/>
+      <c r="T18" s="30"/>
+      <c r="U18" s="30"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="30"/>
+      <c r="X18" s="30"/>
+      <c r="Y18" s="30"/>
+      <c r="Z18" s="30"/>
+      <c r="AA18" s="30"/>
+      <c r="AB18" s="30"/>
+      <c r="AC18" s="30"/>
+      <c r="AD18" s="30"/>
+      <c r="AE18" s="30"/>
+      <c r="AF18" s="30"/>
+      <c r="AG18" s="30"/>
+      <c r="AH18" s="30"/>
+      <c r="AI18" s="30"/>
+      <c r="AJ18" s="30"/>
+      <c r="AK18" s="30"/>
+      <c r="AL18" s="30"/>
+      <c r="AM18" s="30"/>
+      <c r="AN18" s="30"/>
+      <c r="AO18" s="30"/>
+      <c r="AP18" s="30"/>
+      <c r="AQ18" s="30"/>
+      <c r="AR18" s="30"/>
+      <c r="AS18" s="30"/>
+      <c r="AT18" s="30"/>
+      <c r="AU18" s="30"/>
+      <c r="AV18" s="30"/>
+      <c r="AW18" s="30"/>
+      <c r="AX18" s="30"/>
+      <c r="AY18" s="30"/>
+      <c r="AZ18" s="30"/>
+      <c r="BA18" s="30"/>
+      <c r="BB18" s="30"/>
+      <c r="BC18" s="30"/>
+      <c r="BD18" s="30"/>
+      <c r="BE18" s="30"/>
+      <c r="BF18" s="30"/>
+      <c r="BG18" s="30"/>
+      <c r="BH18" s="30"/>
+      <c r="BI18" s="30"/>
+      <c r="BJ18" s="30"/>
+      <c r="BK18" s="30"/>
+      <c r="BL18" s="30"/>
+      <c r="BM18" s="30"/>
+      <c r="BN18" s="30"/>
+      <c r="BO18" s="30"/>
+      <c r="BP18" s="32"/>
       <c r="BQ18" s="6"/>
     </row>
     <row r="19" spans="2:69" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1499,73 +1503,73 @@
       <c r="BQ19" s="6"/>
     </row>
     <row r="20" spans="2:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
-      <c r="I20" s="8"/>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="8"/>
-      <c r="S20" s="8"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="8"/>
-      <c r="V20" s="8"/>
-      <c r="W20" s="8"/>
-      <c r="X20" s="8"/>
-      <c r="Y20" s="8"/>
-      <c r="Z20" s="8"/>
-      <c r="AA20" s="8"/>
-      <c r="AB20" s="8"/>
-      <c r="AC20" s="8"/>
-      <c r="AD20" s="8"/>
-      <c r="AE20" s="8"/>
-      <c r="AF20" s="8"/>
-      <c r="AG20" s="8"/>
-      <c r="AH20" s="8"/>
-      <c r="AI20" s="8"/>
-      <c r="AJ20" s="8"/>
-      <c r="AK20" s="8"/>
-      <c r="AL20" s="8"/>
-      <c r="AM20" s="8"/>
-      <c r="AN20" s="8"/>
-      <c r="AO20" s="8"/>
-      <c r="AP20" s="8"/>
-      <c r="AQ20" s="8"/>
-      <c r="AR20" s="8"/>
-      <c r="AS20" s="8"/>
-      <c r="AT20" s="8"/>
-      <c r="AU20" s="8"/>
-      <c r="AV20" s="8"/>
-      <c r="AW20" s="8"/>
-      <c r="AX20" s="8"/>
-      <c r="AY20" s="8"/>
-      <c r="AZ20" s="8"/>
-      <c r="BA20" s="8"/>
-      <c r="BB20" s="8"/>
-      <c r="BC20" s="8"/>
-      <c r="BD20" s="8"/>
-      <c r="BE20" s="8"/>
-      <c r="BF20" s="8"/>
-      <c r="BG20" s="8"/>
-      <c r="BH20" s="8"/>
-      <c r="BI20" s="8"/>
-      <c r="BJ20" s="8"/>
-      <c r="BK20" s="8"/>
-      <c r="BL20" s="8"/>
-      <c r="BM20" s="8"/>
-      <c r="BN20" s="8"/>
-      <c r="BO20" s="8"/>
-      <c r="BP20" s="8"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
+      <c r="AA20" s="30"/>
+      <c r="AB20" s="30"/>
+      <c r="AC20" s="30"/>
+      <c r="AD20" s="30"/>
+      <c r="AE20" s="30"/>
+      <c r="AF20" s="30"/>
+      <c r="AG20" s="30"/>
+      <c r="AH20" s="30"/>
+      <c r="AI20" s="30"/>
+      <c r="AJ20" s="30"/>
+      <c r="AK20" s="30"/>
+      <c r="AL20" s="30"/>
+      <c r="AM20" s="30"/>
+      <c r="AN20" s="30"/>
+      <c r="AO20" s="30"/>
+      <c r="AP20" s="30"/>
+      <c r="AQ20" s="30"/>
+      <c r="AR20" s="30"/>
+      <c r="AS20" s="30"/>
+      <c r="AT20" s="30"/>
+      <c r="AU20" s="30"/>
+      <c r="AV20" s="30"/>
+      <c r="AW20" s="30"/>
+      <c r="AX20" s="30"/>
+      <c r="AY20" s="30"/>
+      <c r="AZ20" s="30"/>
+      <c r="BA20" s="30"/>
+      <c r="BB20" s="30"/>
+      <c r="BC20" s="30"/>
+      <c r="BD20" s="30"/>
+      <c r="BE20" s="30"/>
+      <c r="BF20" s="30"/>
+      <c r="BG20" s="30"/>
+      <c r="BH20" s="30"/>
+      <c r="BI20" s="30"/>
+      <c r="BJ20" s="30"/>
+      <c r="BK20" s="30"/>
+      <c r="BL20" s="30"/>
+      <c r="BM20" s="30"/>
+      <c r="BN20" s="30"/>
+      <c r="BO20" s="30"/>
+      <c r="BP20" s="32"/>
       <c r="BQ20" s="6"/>
     </row>
     <row r="21" spans="2:69" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1639,73 +1643,73 @@
       <c r="BQ21" s="1"/>
     </row>
     <row r="22" spans="2:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
-      <c r="I22" s="8"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="8"/>
-      <c r="S22" s="8"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="8"/>
-      <c r="V22" s="8"/>
-      <c r="W22" s="8"/>
-      <c r="X22" s="8"/>
-      <c r="Y22" s="8"/>
-      <c r="Z22" s="8"/>
-      <c r="AA22" s="8"/>
-      <c r="AB22" s="8"/>
-      <c r="AC22" s="8"/>
-      <c r="AD22" s="8"/>
-      <c r="AE22" s="8"/>
-      <c r="AF22" s="8"/>
-      <c r="AG22" s="8"/>
-      <c r="AH22" s="8"/>
-      <c r="AI22" s="8"/>
-      <c r="AJ22" s="8"/>
-      <c r="AK22" s="8"/>
-      <c r="AL22" s="8"/>
-      <c r="AM22" s="8"/>
-      <c r="AN22" s="8"/>
-      <c r="AO22" s="8"/>
-      <c r="AP22" s="8"/>
-      <c r="AQ22" s="8"/>
-      <c r="AR22" s="8"/>
-      <c r="AS22" s="8"/>
-      <c r="AT22" s="8"/>
-      <c r="AU22" s="8"/>
-      <c r="AV22" s="8"/>
-      <c r="AW22" s="8"/>
-      <c r="AX22" s="8"/>
-      <c r="AY22" s="8"/>
-      <c r="AZ22" s="8"/>
-      <c r="BA22" s="8"/>
-      <c r="BB22" s="8"/>
-      <c r="BC22" s="8"/>
-      <c r="BD22" s="8"/>
-      <c r="BE22" s="8"/>
-      <c r="BF22" s="8"/>
-      <c r="BG22" s="8"/>
-      <c r="BH22" s="8"/>
-      <c r="BI22" s="8"/>
-      <c r="BJ22" s="8"/>
-      <c r="BK22" s="8"/>
-      <c r="BL22" s="8"/>
-      <c r="BM22" s="8"/>
-      <c r="BN22" s="8"/>
-      <c r="BO22" s="8"/>
-      <c r="BP22" s="8"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="30"/>
+      <c r="E22" s="30"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="30"/>
+      <c r="O22" s="30"/>
+      <c r="P22" s="30"/>
+      <c r="Q22" s="30"/>
+      <c r="R22" s="30"/>
+      <c r="S22" s="30"/>
+      <c r="T22" s="30"/>
+      <c r="U22" s="30"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="30"/>
+      <c r="X22" s="30"/>
+      <c r="Y22" s="30"/>
+      <c r="Z22" s="30"/>
+      <c r="AA22" s="30"/>
+      <c r="AB22" s="30"/>
+      <c r="AC22" s="30"/>
+      <c r="AD22" s="30"/>
+      <c r="AE22" s="30"/>
+      <c r="AF22" s="30"/>
+      <c r="AG22" s="30"/>
+      <c r="AH22" s="30"/>
+      <c r="AI22" s="30"/>
+      <c r="AJ22" s="30"/>
+      <c r="AK22" s="30"/>
+      <c r="AL22" s="30"/>
+      <c r="AM22" s="30"/>
+      <c r="AN22" s="30"/>
+      <c r="AO22" s="30"/>
+      <c r="AP22" s="30"/>
+      <c r="AQ22" s="30"/>
+      <c r="AR22" s="30"/>
+      <c r="AS22" s="30"/>
+      <c r="AT22" s="30"/>
+      <c r="AU22" s="30"/>
+      <c r="AV22" s="30"/>
+      <c r="AW22" s="30"/>
+      <c r="AX22" s="30"/>
+      <c r="AY22" s="30"/>
+      <c r="AZ22" s="30"/>
+      <c r="BA22" s="30"/>
+      <c r="BB22" s="30"/>
+      <c r="BC22" s="30"/>
+      <c r="BD22" s="30"/>
+      <c r="BE22" s="30"/>
+      <c r="BF22" s="30"/>
+      <c r="BG22" s="30"/>
+      <c r="BH22" s="30"/>
+      <c r="BI22" s="30"/>
+      <c r="BJ22" s="30"/>
+      <c r="BK22" s="30"/>
+      <c r="BL22" s="30"/>
+      <c r="BM22" s="30"/>
+      <c r="BN22" s="30"/>
+      <c r="BO22" s="30"/>
+      <c r="BP22" s="32"/>
       <c r="BQ22" s="1"/>
     </row>
     <row r="23" spans="2:69" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1779,73 +1783,73 @@
       <c r="BQ23" s="1"/>
     </row>
     <row r="24" spans="2:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
-      <c r="S24" s="8"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="8"/>
-      <c r="V24" s="8"/>
-      <c r="W24" s="8"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="8"/>
-      <c r="Z24" s="8"/>
-      <c r="AA24" s="8"/>
-      <c r="AB24" s="8"/>
-      <c r="AC24" s="8"/>
-      <c r="AD24" s="8"/>
-      <c r="AE24" s="8"/>
-      <c r="AF24" s="8"/>
-      <c r="AG24" s="8"/>
-      <c r="AH24" s="8"/>
-      <c r="AI24" s="8"/>
-      <c r="AJ24" s="8"/>
-      <c r="AK24" s="8"/>
-      <c r="AL24" s="8"/>
-      <c r="AM24" s="8"/>
-      <c r="AN24" s="8"/>
-      <c r="AO24" s="8"/>
-      <c r="AP24" s="8"/>
-      <c r="AQ24" s="8"/>
-      <c r="AR24" s="8"/>
-      <c r="AS24" s="8"/>
-      <c r="AT24" s="8"/>
-      <c r="AU24" s="8"/>
-      <c r="AV24" s="8"/>
-      <c r="AW24" s="8"/>
-      <c r="AX24" s="8"/>
-      <c r="AY24" s="8"/>
-      <c r="AZ24" s="8"/>
-      <c r="BA24" s="8"/>
-      <c r="BB24" s="8"/>
-      <c r="BC24" s="8"/>
-      <c r="BD24" s="8"/>
-      <c r="BE24" s="8"/>
-      <c r="BF24" s="8"/>
-      <c r="BG24" s="8"/>
-      <c r="BH24" s="8"/>
-      <c r="BI24" s="8"/>
-      <c r="BJ24" s="8"/>
-      <c r="BK24" s="8"/>
-      <c r="BL24" s="8"/>
-      <c r="BM24" s="8"/>
-      <c r="BN24" s="8"/>
-      <c r="BO24" s="8"/>
-      <c r="BP24" s="8"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="30"/>
+      <c r="P24" s="30"/>
+      <c r="Q24" s="30"/>
+      <c r="R24" s="30"/>
+      <c r="S24" s="30"/>
+      <c r="T24" s="30"/>
+      <c r="U24" s="30"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="30"/>
+      <c r="X24" s="30"/>
+      <c r="Y24" s="30"/>
+      <c r="Z24" s="30"/>
+      <c r="AA24" s="30"/>
+      <c r="AB24" s="30"/>
+      <c r="AC24" s="30"/>
+      <c r="AD24" s="30"/>
+      <c r="AE24" s="30"/>
+      <c r="AF24" s="30"/>
+      <c r="AG24" s="30"/>
+      <c r="AH24" s="30"/>
+      <c r="AI24" s="30"/>
+      <c r="AJ24" s="30"/>
+      <c r="AK24" s="30"/>
+      <c r="AL24" s="30"/>
+      <c r="AM24" s="30"/>
+      <c r="AN24" s="30"/>
+      <c r="AO24" s="30"/>
+      <c r="AP24" s="30"/>
+      <c r="AQ24" s="30"/>
+      <c r="AR24" s="30"/>
+      <c r="AS24" s="30"/>
+      <c r="AT24" s="30"/>
+      <c r="AU24" s="30"/>
+      <c r="AV24" s="30"/>
+      <c r="AW24" s="30"/>
+      <c r="AX24" s="30"/>
+      <c r="AY24" s="30"/>
+      <c r="AZ24" s="30"/>
+      <c r="BA24" s="30"/>
+      <c r="BB24" s="30"/>
+      <c r="BC24" s="30"/>
+      <c r="BD24" s="30"/>
+      <c r="BE24" s="30"/>
+      <c r="BF24" s="30"/>
+      <c r="BG24" s="30"/>
+      <c r="BH24" s="30"/>
+      <c r="BI24" s="30"/>
+      <c r="BJ24" s="30"/>
+      <c r="BK24" s="30"/>
+      <c r="BL24" s="30"/>
+      <c r="BM24" s="30"/>
+      <c r="BN24" s="30"/>
+      <c r="BO24" s="30"/>
+      <c r="BP24" s="32"/>
     </row>
     <row r="25" spans="2:69" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1"/>
@@ -1872,7 +1876,7 @@
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-      <c r="P26" s="23"/>
+      <c r="P26" s="33"/>
       <c r="Q26" s="23"/>
       <c r="R26" s="23"/>
       <c r="S26" s="23"/>
@@ -1885,27 +1889,27 @@
       <c r="Z26" s="23"/>
       <c r="AA26" s="23"/>
       <c r="AB26" s="22"/>
-      <c r="AC26" s="3" t="s">
+      <c r="AC26" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="AD26" s="3"/>
-      <c r="AE26" s="3"/>
-      <c r="AF26" s="3"/>
-      <c r="AG26" s="3"/>
-      <c r="AH26" s="3"/>
-      <c r="AI26" s="3"/>
-      <c r="AJ26" s="3"/>
-      <c r="AK26" s="3"/>
-      <c r="AL26" s="3"/>
-      <c r="AM26" s="3"/>
-      <c r="AN26" s="3"/>
-      <c r="AO26" s="3"/>
-      <c r="AP26" s="3"/>
-      <c r="AQ26" s="3"/>
-      <c r="AR26" s="3"/>
-      <c r="AS26" s="3"/>
-      <c r="AT26" s="3"/>
-      <c r="AU26" s="23"/>
+      <c r="AD26" s="2"/>
+      <c r="AE26" s="2"/>
+      <c r="AF26" s="2"/>
+      <c r="AG26" s="2"/>
+      <c r="AH26" s="2"/>
+      <c r="AI26" s="2"/>
+      <c r="AJ26" s="2"/>
+      <c r="AK26" s="2"/>
+      <c r="AL26" s="2"/>
+      <c r="AM26" s="2"/>
+      <c r="AN26" s="2"/>
+      <c r="AO26" s="2"/>
+      <c r="AP26" s="2"/>
+      <c r="AQ26" s="2"/>
+      <c r="AR26" s="2"/>
+      <c r="AS26" s="2"/>
+      <c r="AT26" s="2"/>
+      <c r="AU26" s="2"/>
       <c r="AV26" s="23"/>
       <c r="AW26" s="23"/>
       <c r="AX26" s="23"/>
@@ -1916,11 +1920,10 @@
       <c r="BC26" s="23"/>
       <c r="BD26" s="23"/>
       <c r="BE26" s="23"/>
-      <c r="BF26" s="23"/>
+      <c r="BF26" s="22"/>
       <c r="BG26" s="22"/>
       <c r="BH26" s="22"/>
       <c r="BI26" s="22"/>
-      <c r="BJ26" s="22"/>
     </row>
     <row r="27" spans="2:69" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
@@ -1973,20 +1976,20 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="9"/>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9"/>
-      <c r="P32" s="9"/>
-      <c r="Q32" s="9"/>
-      <c r="R32" s="9"/>
-      <c r="S32" s="9"/>
-      <c r="T32" s="9"/>
-      <c r="U32" s="9"/>
-    </row>
-    <row r="33" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
+      <c r="U32" s="7"/>
+    </row>
+    <row r="33" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -1994,150 +1997,146 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="2:57" x14ac:dyDescent="0.25">
-      <c r="M34" s="16" t="s">
+    <row r="34" spans="2:56" x14ac:dyDescent="0.25">
+      <c r="M34" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="N34" s="17"/>
-      <c r="O34" s="17"/>
-      <c r="P34" s="17"/>
-      <c r="Q34" s="17"/>
-      <c r="R34" s="17"/>
-      <c r="S34" s="17"/>
-      <c r="T34" s="17"/>
-      <c r="U34" s="17"/>
-      <c r="V34" s="17"/>
-      <c r="W34" s="17"/>
-      <c r="X34" s="17"/>
-      <c r="Y34" s="17"/>
-      <c r="Z34" s="17"/>
-      <c r="AA34" s="17"/>
-      <c r="AB34" s="18"/>
-      <c r="AP34" s="16" t="s">
+      <c r="N34" s="15"/>
+      <c r="O34" s="15"/>
+      <c r="P34" s="15"/>
+      <c r="Q34" s="15"/>
+      <c r="R34" s="15"/>
+      <c r="S34" s="15"/>
+      <c r="T34" s="15"/>
+      <c r="U34" s="15"/>
+      <c r="V34" s="15"/>
+      <c r="W34" s="15"/>
+      <c r="X34" s="15"/>
+      <c r="Y34" s="15"/>
+      <c r="Z34" s="15"/>
+      <c r="AA34" s="15"/>
+      <c r="AB34" s="16"/>
+      <c r="AP34" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="AQ34" s="17"/>
-      <c r="AR34" s="17"/>
-      <c r="AS34" s="17"/>
-      <c r="AT34" s="17"/>
-      <c r="AU34" s="17"/>
-      <c r="AV34" s="17"/>
-      <c r="AW34" s="17"/>
-      <c r="AX34" s="17"/>
-      <c r="AY34" s="17"/>
-      <c r="AZ34" s="17"/>
-      <c r="BA34" s="17"/>
-      <c r="BB34" s="17"/>
-      <c r="BC34" s="17"/>
-      <c r="BD34" s="17"/>
-      <c r="BE34" s="18"/>
-    </row>
-    <row r="35" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="AQ34" s="15"/>
+      <c r="AR34" s="15"/>
+      <c r="AS34" s="15"/>
+      <c r="AT34" s="15"/>
+      <c r="AU34" s="15"/>
+      <c r="AV34" s="15"/>
+      <c r="AW34" s="15"/>
+      <c r="AX34" s="15"/>
+      <c r="AY34" s="15"/>
+      <c r="AZ34" s="15"/>
+      <c r="BA34" s="15"/>
+      <c r="BB34" s="15"/>
+      <c r="BC34" s="15"/>
+      <c r="BD34" s="16"/>
+    </row>
+    <row r="35" spans="2:56" x14ac:dyDescent="0.25">
       <c r="M35" s="24"/>
       <c r="N35" s="25"/>
-      <c r="O35" s="11"/>
-      <c r="P35" s="11"/>
-      <c r="Q35" s="11"/>
-      <c r="R35" s="11"/>
-      <c r="S35" s="11"/>
-      <c r="T35" s="11"/>
-      <c r="U35" s="11"/>
-      <c r="V35" s="11"/>
-      <c r="W35" s="11"/>
-      <c r="X35" s="11"/>
-      <c r="Y35" s="11"/>
-      <c r="Z35" s="11"/>
-      <c r="AA35" s="11"/>
-      <c r="AB35" s="12"/>
-      <c r="AP35" s="10"/>
-      <c r="AQ35" s="11"/>
-      <c r="AR35" s="11"/>
-      <c r="AS35" s="11"/>
-      <c r="AT35" s="11"/>
-      <c r="AU35" s="11"/>
-      <c r="AV35" s="11"/>
-      <c r="AW35" s="11"/>
-      <c r="AX35" s="11"/>
-      <c r="AY35" s="11"/>
-      <c r="AZ35" s="11"/>
-      <c r="BA35" s="11"/>
-      <c r="BB35" s="11"/>
-      <c r="BC35" s="11"/>
-      <c r="BD35" s="25"/>
-      <c r="BE35" s="28"/>
-    </row>
-    <row r="36" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="O35" s="9"/>
+      <c r="P35" s="9"/>
+      <c r="Q35" s="9"/>
+      <c r="R35" s="9"/>
+      <c r="S35" s="9"/>
+      <c r="T35" s="9"/>
+      <c r="U35" s="9"/>
+      <c r="V35" s="9"/>
+      <c r="W35" s="9"/>
+      <c r="X35" s="9"/>
+      <c r="Y35" s="9"/>
+      <c r="Z35" s="9"/>
+      <c r="AA35" s="9"/>
+      <c r="AB35" s="10"/>
+      <c r="AP35" s="8"/>
+      <c r="AQ35" s="9"/>
+      <c r="AR35" s="9"/>
+      <c r="AS35" s="9"/>
+      <c r="AT35" s="9"/>
+      <c r="AU35" s="9"/>
+      <c r="AV35" s="9"/>
+      <c r="AW35" s="9"/>
+      <c r="AX35" s="9"/>
+      <c r="AY35" s="9"/>
+      <c r="AZ35" s="9"/>
+      <c r="BA35" s="9"/>
+      <c r="BB35" s="9"/>
+      <c r="BC35" s="9"/>
+      <c r="BD35" s="28"/>
+    </row>
+    <row r="36" spans="2:56" x14ac:dyDescent="0.25">
       <c r="M36" s="24"/>
       <c r="N36" s="25"/>
-      <c r="O36" s="11"/>
-      <c r="P36" s="11"/>
-      <c r="Q36" s="11"/>
-      <c r="R36" s="11"/>
-      <c r="S36" s="11"/>
-      <c r="T36" s="11"/>
-      <c r="U36" s="11"/>
-      <c r="V36" s="11"/>
-      <c r="W36" s="11"/>
-      <c r="X36" s="11"/>
-      <c r="Y36" s="11"/>
-      <c r="Z36" s="11"/>
-      <c r="AA36" s="11"/>
-      <c r="AB36" s="12"/>
-      <c r="AP36" s="10"/>
-      <c r="AQ36" s="11"/>
-      <c r="AR36" s="11"/>
-      <c r="AS36" s="11"/>
-      <c r="AT36" s="11"/>
-      <c r="AU36" s="11"/>
-      <c r="AV36" s="11"/>
-      <c r="AW36" s="11"/>
-      <c r="AX36" s="11"/>
-      <c r="AY36" s="11"/>
-      <c r="AZ36" s="11"/>
-      <c r="BA36" s="11"/>
-      <c r="BB36" s="11"/>
-      <c r="BC36" s="11"/>
-      <c r="BD36" s="25"/>
-      <c r="BE36" s="28"/>
-    </row>
-    <row r="37" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="O36" s="9"/>
+      <c r="P36" s="9"/>
+      <c r="Q36" s="9"/>
+      <c r="R36" s="9"/>
+      <c r="S36" s="9"/>
+      <c r="T36" s="9"/>
+      <c r="U36" s="9"/>
+      <c r="V36" s="9"/>
+      <c r="W36" s="9"/>
+      <c r="X36" s="9"/>
+      <c r="Y36" s="9"/>
+      <c r="Z36" s="9"/>
+      <c r="AA36" s="9"/>
+      <c r="AB36" s="10"/>
+      <c r="AP36" s="8"/>
+      <c r="AQ36" s="9"/>
+      <c r="AR36" s="9"/>
+      <c r="AS36" s="9"/>
+      <c r="AT36" s="9"/>
+      <c r="AU36" s="9"/>
+      <c r="AV36" s="9"/>
+      <c r="AW36" s="9"/>
+      <c r="AX36" s="9"/>
+      <c r="AY36" s="9"/>
+      <c r="AZ36" s="9"/>
+      <c r="BA36" s="9"/>
+      <c r="BB36" s="9"/>
+      <c r="BC36" s="9"/>
+      <c r="BD36" s="28"/>
+    </row>
+    <row r="37" spans="2:56" x14ac:dyDescent="0.25">
       <c r="M37" s="26"/>
       <c r="N37" s="27"/>
-      <c r="O37" s="14"/>
-      <c r="P37" s="14"/>
-      <c r="Q37" s="14"/>
-      <c r="R37" s="14"/>
-      <c r="S37" s="14"/>
-      <c r="T37" s="14"/>
-      <c r="U37" s="14"/>
-      <c r="V37" s="14"/>
-      <c r="W37" s="14"/>
-      <c r="X37" s="14"/>
-      <c r="Y37" s="14"/>
-      <c r="Z37" s="14"/>
-      <c r="AA37" s="14"/>
-      <c r="AB37" s="15"/>
-      <c r="AP37" s="13"/>
-      <c r="AQ37" s="14"/>
-      <c r="AR37" s="14"/>
-      <c r="AS37" s="14"/>
-      <c r="AT37" s="14"/>
-      <c r="AU37" s="14"/>
-      <c r="AV37" s="14"/>
-      <c r="AW37" s="14"/>
-      <c r="AX37" s="14"/>
-      <c r="AY37" s="14"/>
-      <c r="AZ37" s="14"/>
-      <c r="BA37" s="14"/>
-      <c r="BB37" s="14"/>
-      <c r="BC37" s="14"/>
-      <c r="BD37" s="27"/>
-      <c r="BE37" s="29"/>
-    </row>
-    <row r="38" spans="2:57" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="2:57" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" spans="2:57" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="O37" s="12"/>
+      <c r="P37" s="12"/>
+      <c r="Q37" s="12"/>
+      <c r="R37" s="12"/>
+      <c r="S37" s="12"/>
+      <c r="T37" s="12"/>
+      <c r="U37" s="12"/>
+      <c r="V37" s="12"/>
+      <c r="W37" s="12"/>
+      <c r="X37" s="12"/>
+      <c r="Y37" s="12"/>
+      <c r="Z37" s="12"/>
+      <c r="AA37" s="12"/>
+      <c r="AB37" s="13"/>
+      <c r="AP37" s="11"/>
+      <c r="AQ37" s="12"/>
+      <c r="AR37" s="12"/>
+      <c r="AS37" s="12"/>
+      <c r="AT37" s="12"/>
+      <c r="AU37" s="12"/>
+      <c r="AV37" s="12"/>
+      <c r="AW37" s="12"/>
+      <c r="AX37" s="12"/>
+      <c r="AY37" s="12"/>
+      <c r="AZ37" s="12"/>
+      <c r="BA37" s="12"/>
+      <c r="BB37" s="12"/>
+      <c r="BC37" s="12"/>
+      <c r="BD37" s="29"/>
+    </row>
+    <row r="38" spans="2:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="2:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="2:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B42" s="3" t="s">
         <v>12</v>
       </c>
@@ -2163,317 +2162,313 @@
       <c r="V42" s="23"/>
       <c r="W42" s="23"/>
     </row>
-    <row r="44" spans="2:57" x14ac:dyDescent="0.25">
-      <c r="M44" s="16" t="s">
+    <row r="44" spans="2:56" x14ac:dyDescent="0.25">
+      <c r="M44" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="N44" s="17"/>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-      <c r="R44" s="17"/>
-      <c r="S44" s="17"/>
-      <c r="T44" s="17"/>
-      <c r="U44" s="17"/>
-      <c r="V44" s="17"/>
-      <c r="W44" s="17"/>
-      <c r="X44" s="17"/>
-      <c r="Y44" s="17"/>
-      <c r="Z44" s="17"/>
-      <c r="AA44" s="17"/>
-      <c r="AB44" s="18"/>
-      <c r="AP44" s="16" t="s">
+      <c r="N44" s="15"/>
+      <c r="O44" s="15"/>
+      <c r="P44" s="15"/>
+      <c r="Q44" s="15"/>
+      <c r="R44" s="15"/>
+      <c r="S44" s="15"/>
+      <c r="T44" s="15"/>
+      <c r="U44" s="15"/>
+      <c r="V44" s="15"/>
+      <c r="W44" s="15"/>
+      <c r="X44" s="15"/>
+      <c r="Y44" s="15"/>
+      <c r="Z44" s="15"/>
+      <c r="AA44" s="15"/>
+      <c r="AB44" s="16"/>
+      <c r="AP44" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="AQ44" s="17"/>
-      <c r="AR44" s="17"/>
-      <c r="AS44" s="17"/>
-      <c r="AT44" s="17"/>
-      <c r="AU44" s="17"/>
-      <c r="AV44" s="17"/>
-      <c r="AW44" s="17"/>
-      <c r="AX44" s="17"/>
-      <c r="AY44" s="17"/>
-      <c r="AZ44" s="17"/>
-      <c r="BA44" s="17"/>
-      <c r="BB44" s="17"/>
-      <c r="BC44" s="17"/>
-      <c r="BD44" s="17"/>
-      <c r="BE44" s="18"/>
-    </row>
-    <row r="45" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="AQ44" s="15"/>
+      <c r="AR44" s="15"/>
+      <c r="AS44" s="15"/>
+      <c r="AT44" s="15"/>
+      <c r="AU44" s="15"/>
+      <c r="AV44" s="15"/>
+      <c r="AW44" s="15"/>
+      <c r="AX44" s="15"/>
+      <c r="AY44" s="15"/>
+      <c r="AZ44" s="15"/>
+      <c r="BA44" s="15"/>
+      <c r="BB44" s="15"/>
+      <c r="BC44" s="15"/>
+      <c r="BD44" s="16"/>
+    </row>
+    <row r="45" spans="2:56" x14ac:dyDescent="0.25">
       <c r="M45" s="24"/>
       <c r="N45" s="25"/>
-      <c r="O45" s="11"/>
-      <c r="P45" s="11"/>
-      <c r="Q45" s="11"/>
-      <c r="R45" s="11"/>
-      <c r="S45" s="11"/>
-      <c r="T45" s="11"/>
-      <c r="U45" s="11"/>
-      <c r="V45" s="11"/>
-      <c r="W45" s="11"/>
-      <c r="X45" s="11"/>
-      <c r="Y45" s="11"/>
-      <c r="Z45" s="11"/>
-      <c r="AA45" s="11"/>
-      <c r="AB45" s="12"/>
-      <c r="AP45" s="10"/>
-      <c r="AQ45" s="11"/>
-      <c r="AR45" s="11"/>
-      <c r="AS45" s="11"/>
-      <c r="AT45" s="11"/>
-      <c r="AU45" s="11"/>
-      <c r="AV45" s="11"/>
-      <c r="AW45" s="11"/>
-      <c r="AX45" s="11"/>
-      <c r="AY45" s="11"/>
-      <c r="AZ45" s="11"/>
-      <c r="BA45" s="11"/>
-      <c r="BB45" s="11"/>
-      <c r="BC45" s="11"/>
-      <c r="BD45" s="25"/>
-      <c r="BE45" s="28"/>
-    </row>
-    <row r="46" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="O45" s="9"/>
+      <c r="P45" s="9"/>
+      <c r="Q45" s="9"/>
+      <c r="R45" s="9"/>
+      <c r="S45" s="9"/>
+      <c r="T45" s="9"/>
+      <c r="U45" s="9"/>
+      <c r="V45" s="9"/>
+      <c r="W45" s="9"/>
+      <c r="X45" s="9"/>
+      <c r="Y45" s="9"/>
+      <c r="Z45" s="9"/>
+      <c r="AA45" s="9"/>
+      <c r="AB45" s="10"/>
+      <c r="AP45" s="8"/>
+      <c r="AQ45" s="9"/>
+      <c r="AR45" s="9"/>
+      <c r="AS45" s="9"/>
+      <c r="AT45" s="9"/>
+      <c r="AU45" s="9"/>
+      <c r="AV45" s="9"/>
+      <c r="AW45" s="9"/>
+      <c r="AX45" s="9"/>
+      <c r="AY45" s="9"/>
+      <c r="AZ45" s="9"/>
+      <c r="BA45" s="9"/>
+      <c r="BB45" s="9"/>
+      <c r="BC45" s="9"/>
+      <c r="BD45" s="28"/>
+    </row>
+    <row r="46" spans="2:56" x14ac:dyDescent="0.25">
       <c r="M46" s="24"/>
       <c r="N46" s="25"/>
-      <c r="O46" s="11"/>
-      <c r="P46" s="11"/>
-      <c r="Q46" s="11"/>
-      <c r="R46" s="11"/>
-      <c r="S46" s="11"/>
-      <c r="T46" s="11"/>
-      <c r="U46" s="11"/>
-      <c r="V46" s="11"/>
-      <c r="W46" s="11"/>
-      <c r="X46" s="11"/>
-      <c r="Y46" s="11"/>
-      <c r="Z46" s="11"/>
-      <c r="AA46" s="11"/>
-      <c r="AB46" s="12"/>
-      <c r="AP46" s="10"/>
-      <c r="AQ46" s="11"/>
-      <c r="AR46" s="11"/>
-      <c r="AS46" s="11"/>
-      <c r="AT46" s="11"/>
-      <c r="AU46" s="11"/>
-      <c r="AV46" s="11"/>
-      <c r="AW46" s="11"/>
-      <c r="AX46" s="11"/>
-      <c r="AY46" s="11"/>
-      <c r="AZ46" s="11"/>
-      <c r="BA46" s="11"/>
-      <c r="BB46" s="11"/>
-      <c r="BC46" s="11"/>
-      <c r="BD46" s="25"/>
-      <c r="BE46" s="28"/>
-    </row>
-    <row r="47" spans="2:57" x14ac:dyDescent="0.25">
+      <c r="O46" s="9"/>
+      <c r="P46" s="9"/>
+      <c r="Q46" s="9"/>
+      <c r="R46" s="9"/>
+      <c r="S46" s="9"/>
+      <c r="T46" s="9"/>
+      <c r="U46" s="9"/>
+      <c r="V46" s="9"/>
+      <c r="W46" s="9"/>
+      <c r="X46" s="9"/>
+      <c r="Y46" s="9"/>
+      <c r="Z46" s="9"/>
+      <c r="AA46" s="9"/>
+      <c r="AB46" s="10"/>
+      <c r="AP46" s="8"/>
+      <c r="AQ46" s="9"/>
+      <c r="AR46" s="9"/>
+      <c r="AS46" s="9"/>
+      <c r="AT46" s="9"/>
+      <c r="AU46" s="9"/>
+      <c r="AV46" s="9"/>
+      <c r="AW46" s="9"/>
+      <c r="AX46" s="9"/>
+      <c r="AY46" s="9"/>
+      <c r="AZ46" s="9"/>
+      <c r="BA46" s="9"/>
+      <c r="BB46" s="9"/>
+      <c r="BC46" s="9"/>
+      <c r="BD46" s="28"/>
+    </row>
+    <row r="47" spans="2:56" x14ac:dyDescent="0.25">
       <c r="M47" s="26"/>
       <c r="N47" s="27"/>
-      <c r="O47" s="14"/>
-      <c r="P47" s="14"/>
-      <c r="Q47" s="14"/>
-      <c r="R47" s="14"/>
-      <c r="S47" s="14"/>
-      <c r="T47" s="14"/>
-      <c r="U47" s="14"/>
-      <c r="V47" s="14"/>
-      <c r="W47" s="14"/>
-      <c r="X47" s="14"/>
-      <c r="Y47" s="14"/>
-      <c r="Z47" s="14"/>
-      <c r="AA47" s="14"/>
-      <c r="AB47" s="15"/>
-      <c r="AP47" s="13"/>
-      <c r="AQ47" s="14"/>
-      <c r="AR47" s="14"/>
-      <c r="AS47" s="14"/>
-      <c r="AT47" s="14"/>
-      <c r="AU47" s="14"/>
-      <c r="AV47" s="14"/>
-      <c r="AW47" s="14"/>
-      <c r="AX47" s="14"/>
-      <c r="AY47" s="14"/>
-      <c r="AZ47" s="14"/>
-      <c r="BA47" s="14"/>
-      <c r="BB47" s="14"/>
-      <c r="BC47" s="14"/>
-      <c r="BD47" s="27"/>
-      <c r="BE47" s="29"/>
+      <c r="O47" s="12"/>
+      <c r="P47" s="12"/>
+      <c r="Q47" s="12"/>
+      <c r="R47" s="12"/>
+      <c r="S47" s="12"/>
+      <c r="T47" s="12"/>
+      <c r="U47" s="12"/>
+      <c r="V47" s="12"/>
+      <c r="W47" s="12"/>
+      <c r="X47" s="12"/>
+      <c r="Y47" s="12"/>
+      <c r="Z47" s="12"/>
+      <c r="AA47" s="12"/>
+      <c r="AB47" s="13"/>
+      <c r="AP47" s="11"/>
+      <c r="AQ47" s="12"/>
+      <c r="AR47" s="12"/>
+      <c r="AS47" s="12"/>
+      <c r="AT47" s="12"/>
+      <c r="AU47" s="12"/>
+      <c r="AV47" s="12"/>
+      <c r="AW47" s="12"/>
+      <c r="AX47" s="12"/>
+      <c r="AY47" s="12"/>
+      <c r="AZ47" s="12"/>
+      <c r="BA47" s="12"/>
+      <c r="BB47" s="12"/>
+      <c r="BC47" s="12"/>
+      <c r="BD47" s="29"/>
     </row>
     <row r="53" spans="2:68" ht="10.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="2:68" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="20" t="s">
+      <c r="B54" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
-      <c r="G54" s="20"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="20"/>
-      <c r="L54" s="20"/>
-      <c r="M54" s="20"/>
-      <c r="N54" s="20"/>
-      <c r="O54" s="20"/>
-      <c r="P54" s="20"/>
-      <c r="Q54" s="20"/>
-      <c r="R54" s="20"/>
-      <c r="S54" s="20"/>
-      <c r="T54" s="20"/>
-      <c r="U54" s="20"/>
-      <c r="V54" s="20"/>
-      <c r="W54" s="20"/>
-      <c r="X54" s="20"/>
-      <c r="Y54" s="20"/>
-      <c r="Z54" s="20"/>
-      <c r="AA54" s="20"/>
-      <c r="AB54" s="20"/>
-      <c r="AC54" s="20"/>
-      <c r="AD54" s="20"/>
-      <c r="AE54" s="20"/>
-      <c r="AF54" s="20"/>
-      <c r="AG54" s="20"/>
-      <c r="AH54" s="20"/>
-      <c r="AI54" s="20"/>
-      <c r="AJ54" s="20"/>
-      <c r="AK54" s="20"/>
-      <c r="AL54" s="20"/>
-      <c r="AM54" s="20"/>
-      <c r="AN54" s="20"/>
-      <c r="AO54" s="20"/>
-      <c r="AP54" s="20"/>
-      <c r="AQ54" s="20"/>
-      <c r="AR54" s="20"/>
-      <c r="AS54" s="20"/>
-      <c r="AT54" s="20"/>
-      <c r="AU54" s="20"/>
-      <c r="AV54" s="20"/>
-      <c r="AW54" s="20"/>
-      <c r="AX54" s="20"/>
-      <c r="AY54" s="20"/>
-      <c r="AZ54" s="20"/>
-      <c r="BA54" s="20"/>
-      <c r="BB54" s="20"/>
-      <c r="BC54" s="20"/>
-      <c r="BD54" s="20"/>
-      <c r="BE54" s="20"/>
-      <c r="BF54" s="20"/>
-      <c r="BG54" s="20"/>
-      <c r="BH54" s="20"/>
-      <c r="BI54" s="20"/>
-      <c r="BJ54" s="20"/>
-      <c r="BK54" s="20"/>
-      <c r="BL54" s="20"/>
-      <c r="BM54" s="20"/>
-      <c r="BN54" s="20"/>
-      <c r="BO54" s="20"/>
+      <c r="C54" s="18"/>
+      <c r="D54" s="18"/>
+      <c r="E54" s="18"/>
+      <c r="F54" s="18"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="18"/>
+      <c r="I54" s="18"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="18"/>
+      <c r="M54" s="18"/>
+      <c r="N54" s="18"/>
+      <c r="O54" s="18"/>
+      <c r="P54" s="18"/>
+      <c r="Q54" s="18"/>
+      <c r="R54" s="18"/>
+      <c r="S54" s="18"/>
+      <c r="T54" s="18"/>
+      <c r="U54" s="18"/>
+      <c r="V54" s="18"/>
+      <c r="W54" s="18"/>
+      <c r="X54" s="18"/>
+      <c r="Y54" s="18"/>
+      <c r="Z54" s="18"/>
+      <c r="AA54" s="18"/>
+      <c r="AB54" s="18"/>
+      <c r="AC54" s="18"/>
+      <c r="AD54" s="18"/>
+      <c r="AE54" s="18"/>
+      <c r="AF54" s="18"/>
+      <c r="AG54" s="18"/>
+      <c r="AH54" s="18"/>
+      <c r="AI54" s="18"/>
+      <c r="AJ54" s="18"/>
+      <c r="AK54" s="18"/>
+      <c r="AL54" s="18"/>
+      <c r="AM54" s="18"/>
+      <c r="AN54" s="18"/>
+      <c r="AO54" s="18"/>
+      <c r="AP54" s="18"/>
+      <c r="AQ54" s="18"/>
+      <c r="AR54" s="18"/>
+      <c r="AS54" s="18"/>
+      <c r="AT54" s="18"/>
+      <c r="AU54" s="18"/>
+      <c r="AV54" s="18"/>
+      <c r="AW54" s="18"/>
+      <c r="AX54" s="18"/>
+      <c r="AY54" s="18"/>
+      <c r="AZ54" s="18"/>
+      <c r="BA54" s="18"/>
+      <c r="BB54" s="18"/>
+      <c r="BC54" s="18"/>
+      <c r="BD54" s="18"/>
+      <c r="BE54" s="18"/>
+      <c r="BF54" s="18"/>
+      <c r="BG54" s="18"/>
+      <c r="BH54" s="18"/>
+      <c r="BI54" s="18"/>
+      <c r="BJ54" s="18"/>
+      <c r="BK54" s="18"/>
+      <c r="BL54" s="18"/>
+      <c r="BM54" s="18"/>
+      <c r="BN54" s="18"/>
+      <c r="BO54" s="18"/>
       <c r="BP54" s="20"/>
     </row>
     <row r="55" spans="2:68" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="21" t="s">
+      <c r="B55" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="21"/>
-      <c r="J55" s="21"/>
-      <c r="K55" s="21"/>
-      <c r="L55" s="21"/>
-      <c r="M55" s="21"/>
-      <c r="N55" s="21"/>
-      <c r="O55" s="21"/>
-      <c r="P55" s="21"/>
-      <c r="Q55" s="21"/>
-      <c r="R55" s="21"/>
-      <c r="S55" s="21"/>
-      <c r="T55" s="21"/>
-      <c r="U55" s="21"/>
-      <c r="V55" s="21"/>
-      <c r="W55" s="21"/>
-      <c r="X55" s="21"/>
-      <c r="Y55" s="21"/>
-      <c r="Z55" s="21"/>
-      <c r="AA55" s="21"/>
-      <c r="AB55" s="21"/>
-      <c r="AC55" s="21"/>
-      <c r="AD55" s="21"/>
-      <c r="AE55" s="21"/>
-      <c r="AF55" s="21"/>
-      <c r="AG55" s="21"/>
-      <c r="AH55" s="21"/>
-      <c r="AI55" s="21"/>
-      <c r="AJ55" s="21"/>
-      <c r="AK55" s="21"/>
-      <c r="AL55" s="21"/>
-      <c r="AM55" s="21"/>
-      <c r="AN55" s="21"/>
-      <c r="AO55" s="21"/>
-      <c r="AP55" s="21"/>
-      <c r="AQ55" s="21"/>
-      <c r="AR55" s="21"/>
-      <c r="AS55" s="21"/>
-      <c r="AT55" s="21"/>
-      <c r="AU55" s="21"/>
-      <c r="AV55" s="21"/>
-      <c r="AW55" s="21"/>
-      <c r="AX55" s="21"/>
-      <c r="AY55" s="21"/>
-      <c r="AZ55" s="21"/>
-      <c r="BA55" s="21"/>
-      <c r="BB55" s="21"/>
-      <c r="BC55" s="21"/>
-      <c r="BD55" s="21"/>
-      <c r="BE55" s="21"/>
-      <c r="BF55" s="21"/>
-      <c r="BG55" s="21"/>
-      <c r="BH55" s="21"/>
-      <c r="BI55" s="21"/>
-      <c r="BJ55" s="21"/>
-      <c r="BK55" s="21"/>
-      <c r="BL55" s="21"/>
-      <c r="BM55" s="21"/>
-      <c r="BN55" s="21"/>
-      <c r="BO55" s="21"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="19"/>
+      <c r="H55" s="19"/>
+      <c r="I55" s="19"/>
+      <c r="J55" s="19"/>
+      <c r="K55" s="19"/>
+      <c r="L55" s="19"/>
+      <c r="M55" s="19"/>
+      <c r="N55" s="19"/>
+      <c r="O55" s="19"/>
+      <c r="P55" s="19"/>
+      <c r="Q55" s="19"/>
+      <c r="R55" s="19"/>
+      <c r="S55" s="19"/>
+      <c r="T55" s="19"/>
+      <c r="U55" s="19"/>
+      <c r="V55" s="19"/>
+      <c r="W55" s="19"/>
+      <c r="X55" s="19"/>
+      <c r="Y55" s="19"/>
+      <c r="Z55" s="19"/>
+      <c r="AA55" s="19"/>
+      <c r="AB55" s="19"/>
+      <c r="AC55" s="19"/>
+      <c r="AD55" s="19"/>
+      <c r="AE55" s="19"/>
+      <c r="AF55" s="19"/>
+      <c r="AG55" s="19"/>
+      <c r="AH55" s="19"/>
+      <c r="AI55" s="19"/>
+      <c r="AJ55" s="19"/>
+      <c r="AK55" s="19"/>
+      <c r="AL55" s="19"/>
+      <c r="AM55" s="19"/>
+      <c r="AN55" s="19"/>
+      <c r="AO55" s="19"/>
+      <c r="AP55" s="19"/>
+      <c r="AQ55" s="19"/>
+      <c r="AR55" s="19"/>
+      <c r="AS55" s="19"/>
+      <c r="AT55" s="19"/>
+      <c r="AU55" s="19"/>
+      <c r="AV55" s="19"/>
+      <c r="AW55" s="19"/>
+      <c r="AX55" s="19"/>
+      <c r="AY55" s="19"/>
+      <c r="AZ55" s="19"/>
+      <c r="BA55" s="19"/>
+      <c r="BB55" s="19"/>
+      <c r="BC55" s="19"/>
+      <c r="BD55" s="19"/>
+      <c r="BE55" s="19"/>
+      <c r="BF55" s="19"/>
+      <c r="BG55" s="19"/>
+      <c r="BH55" s="19"/>
+      <c r="BI55" s="19"/>
+      <c r="BJ55" s="19"/>
+      <c r="BK55" s="19"/>
+      <c r="BL55" s="19"/>
+      <c r="BM55" s="19"/>
+      <c r="BN55" s="19"/>
+      <c r="BO55" s="19"/>
       <c r="BP55" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="AV26:BE26"/>
+    <mergeCell ref="P14:Y14"/>
+    <mergeCell ref="Z14:AL14"/>
     <mergeCell ref="B42:K42"/>
     <mergeCell ref="L42:W42"/>
     <mergeCell ref="B32:I32"/>
     <mergeCell ref="J32:U32"/>
     <mergeCell ref="B26:O26"/>
-    <mergeCell ref="P26:AA26"/>
-    <mergeCell ref="AC26:AT26"/>
-    <mergeCell ref="AU26:BF26"/>
-    <mergeCell ref="B8:BP9"/>
-    <mergeCell ref="B54:BP54"/>
-    <mergeCell ref="B55:BP55"/>
+    <mergeCell ref="Q26:AA26"/>
+    <mergeCell ref="AC26:AU26"/>
+    <mergeCell ref="B8:BO9"/>
+    <mergeCell ref="B54:BO54"/>
+    <mergeCell ref="B55:BO55"/>
     <mergeCell ref="M34:AB34"/>
-    <mergeCell ref="AP34:BE34"/>
-    <mergeCell ref="AP44:BE44"/>
+    <mergeCell ref="AP34:BD34"/>
+    <mergeCell ref="AP44:BD44"/>
     <mergeCell ref="M44:AB44"/>
     <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B18:BP18"/>
-    <mergeCell ref="B20:BP20"/>
-    <mergeCell ref="B22:BP22"/>
-    <mergeCell ref="B24:BP24"/>
+    <mergeCell ref="B18:BO18"/>
+    <mergeCell ref="B20:BO20"/>
+    <mergeCell ref="B22:BO22"/>
+    <mergeCell ref="B24:BO24"/>
     <mergeCell ref="B12:U12"/>
-    <mergeCell ref="BH12:BQ12"/>
-    <mergeCell ref="V12:BG12"/>
+    <mergeCell ref="BG12:BQ12"/>
+    <mergeCell ref="V12:BF12"/>
     <mergeCell ref="B14:O14"/>
-    <mergeCell ref="P14:X14"/>
-    <mergeCell ref="Y14:AL14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/templates/request_equipment_template.xlsx
+++ b/templates/request_equipment_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B069E8B-BA22-4A41-864C-3E6458CDD737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADFF5B1-4FB3-4857-B702-72E2F9AD4A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4331DD6E-67AF-48F9-ABB9-6D96E0057117}"/>
   </bookViews>
@@ -220,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -237,9 +237,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -274,18 +271,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -294,6 +285,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -793,144 +790,144 @@
   </cols>
   <sheetData>
     <row r="8" spans="2:69" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17"/>
-      <c r="S8" s="17"/>
-      <c r="T8" s="17"/>
-      <c r="U8" s="17"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="17"/>
-      <c r="Y8" s="17"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="17"/>
-      <c r="AB8" s="17"/>
-      <c r="AC8" s="17"/>
-      <c r="AD8" s="17"/>
-      <c r="AE8" s="17"/>
-      <c r="AF8" s="17"/>
-      <c r="AG8" s="17"/>
-      <c r="AH8" s="17"/>
-      <c r="AI8" s="17"/>
-      <c r="AJ8" s="17"/>
-      <c r="AK8" s="17"/>
-      <c r="AL8" s="17"/>
-      <c r="AM8" s="17"/>
-      <c r="AN8" s="17"/>
-      <c r="AO8" s="17"/>
-      <c r="AP8" s="17"/>
-      <c r="AQ8" s="17"/>
-      <c r="AR8" s="17"/>
-      <c r="AS8" s="17"/>
-      <c r="AT8" s="17"/>
-      <c r="AU8" s="17"/>
-      <c r="AV8" s="17"/>
-      <c r="AW8" s="17"/>
-      <c r="AX8" s="17"/>
-      <c r="AY8" s="17"/>
-      <c r="AZ8" s="17"/>
-      <c r="BA8" s="17"/>
-      <c r="BB8" s="17"/>
-      <c r="BC8" s="17"/>
-      <c r="BD8" s="17"/>
-      <c r="BE8" s="17"/>
-      <c r="BF8" s="17"/>
-      <c r="BG8" s="17"/>
-      <c r="BH8" s="17"/>
-      <c r="BI8" s="17"/>
-      <c r="BJ8" s="17"/>
-      <c r="BK8" s="17"/>
-      <c r="BL8" s="17"/>
-      <c r="BM8" s="17"/>
-      <c r="BN8" s="17"/>
-      <c r="BO8" s="17"/>
-      <c r="BP8" s="31"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16"/>
+      <c r="P8" s="16"/>
+      <c r="Q8" s="16"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="16"/>
+      <c r="V8" s="16"/>
+      <c r="W8" s="16"/>
+      <c r="X8" s="16"/>
+      <c r="Y8" s="16"/>
+      <c r="Z8" s="16"/>
+      <c r="AA8" s="16"/>
+      <c r="AB8" s="16"/>
+      <c r="AC8" s="16"/>
+      <c r="AD8" s="16"/>
+      <c r="AE8" s="16"/>
+      <c r="AF8" s="16"/>
+      <c r="AG8" s="16"/>
+      <c r="AH8" s="16"/>
+      <c r="AI8" s="16"/>
+      <c r="AJ8" s="16"/>
+      <c r="AK8" s="16"/>
+      <c r="AL8" s="16"/>
+      <c r="AM8" s="16"/>
+      <c r="AN8" s="16"/>
+      <c r="AO8" s="16"/>
+      <c r="AP8" s="16"/>
+      <c r="AQ8" s="16"/>
+      <c r="AR8" s="16"/>
+      <c r="AS8" s="16"/>
+      <c r="AT8" s="16"/>
+      <c r="AU8" s="16"/>
+      <c r="AV8" s="16"/>
+      <c r="AW8" s="16"/>
+      <c r="AX8" s="16"/>
+      <c r="AY8" s="16"/>
+      <c r="AZ8" s="16"/>
+      <c r="BA8" s="16"/>
+      <c r="BB8" s="16"/>
+      <c r="BC8" s="16"/>
+      <c r="BD8" s="16"/>
+      <c r="BE8" s="16"/>
+      <c r="BF8" s="16"/>
+      <c r="BG8" s="16"/>
+      <c r="BH8" s="16"/>
+      <c r="BI8" s="16"/>
+      <c r="BJ8" s="16"/>
+      <c r="BK8" s="16"/>
+      <c r="BL8" s="16"/>
+      <c r="BM8" s="16"/>
+      <c r="BN8" s="16"/>
+      <c r="BO8" s="16"/>
+      <c r="BP8" s="28"/>
     </row>
     <row r="9" spans="2:69" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="17"/>
-      <c r="O9" s="17"/>
-      <c r="P9" s="17"/>
-      <c r="Q9" s="17"/>
-      <c r="R9" s="17"/>
-      <c r="S9" s="17"/>
-      <c r="T9" s="17"/>
-      <c r="U9" s="17"/>
-      <c r="V9" s="17"/>
-      <c r="W9" s="17"/>
-      <c r="X9" s="17"/>
-      <c r="Y9" s="17"/>
-      <c r="Z9" s="17"/>
-      <c r="AA9" s="17"/>
-      <c r="AB9" s="17"/>
-      <c r="AC9" s="17"/>
-      <c r="AD9" s="17"/>
-      <c r="AE9" s="17"/>
-      <c r="AF9" s="17"/>
-      <c r="AG9" s="17"/>
-      <c r="AH9" s="17"/>
-      <c r="AI9" s="17"/>
-      <c r="AJ9" s="17"/>
-      <c r="AK9" s="17"/>
-      <c r="AL9" s="17"/>
-      <c r="AM9" s="17"/>
-      <c r="AN9" s="17"/>
-      <c r="AO9" s="17"/>
-      <c r="AP9" s="17"/>
-      <c r="AQ9" s="17"/>
-      <c r="AR9" s="17"/>
-      <c r="AS9" s="17"/>
-      <c r="AT9" s="17"/>
-      <c r="AU9" s="17"/>
-      <c r="AV9" s="17"/>
-      <c r="AW9" s="17"/>
-      <c r="AX9" s="17"/>
-      <c r="AY9" s="17"/>
-      <c r="AZ9" s="17"/>
-      <c r="BA9" s="17"/>
-      <c r="BB9" s="17"/>
-      <c r="BC9" s="17"/>
-      <c r="BD9" s="17"/>
-      <c r="BE9" s="17"/>
-      <c r="BF9" s="17"/>
-      <c r="BG9" s="17"/>
-      <c r="BH9" s="17"/>
-      <c r="BI9" s="17"/>
-      <c r="BJ9" s="17"/>
-      <c r="BK9" s="17"/>
-      <c r="BL9" s="17"/>
-      <c r="BM9" s="17"/>
-      <c r="BN9" s="17"/>
-      <c r="BO9" s="17"/>
-      <c r="BP9" s="31"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="16"/>
+      <c r="P9" s="16"/>
+      <c r="Q9" s="16"/>
+      <c r="R9" s="16"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="16"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="16"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="16"/>
+      <c r="AA9" s="16"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="16"/>
+      <c r="AD9" s="16"/>
+      <c r="AE9" s="16"/>
+      <c r="AF9" s="16"/>
+      <c r="AG9" s="16"/>
+      <c r="AH9" s="16"/>
+      <c r="AI9" s="16"/>
+      <c r="AJ9" s="16"/>
+      <c r="AK9" s="16"/>
+      <c r="AL9" s="16"/>
+      <c r="AM9" s="16"/>
+      <c r="AN9" s="16"/>
+      <c r="AO9" s="16"/>
+      <c r="AP9" s="16"/>
+      <c r="AQ9" s="16"/>
+      <c r="AR9" s="16"/>
+      <c r="AS9" s="16"/>
+      <c r="AT9" s="16"/>
+      <c r="AU9" s="16"/>
+      <c r="AV9" s="16"/>
+      <c r="AW9" s="16"/>
+      <c r="AX9" s="16"/>
+      <c r="AY9" s="16"/>
+      <c r="AZ9" s="16"/>
+      <c r="BA9" s="16"/>
+      <c r="BB9" s="16"/>
+      <c r="BC9" s="16"/>
+      <c r="BD9" s="16"/>
+      <c r="BE9" s="16"/>
+      <c r="BF9" s="16"/>
+      <c r="BG9" s="16"/>
+      <c r="BH9" s="16"/>
+      <c r="BI9" s="16"/>
+      <c r="BJ9" s="16"/>
+      <c r="BK9" s="16"/>
+      <c r="BL9" s="16"/>
+      <c r="BM9" s="16"/>
+      <c r="BN9" s="16"/>
+      <c r="BO9" s="16"/>
+      <c r="BP9" s="28"/>
     </row>
     <row r="12" spans="2:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
@@ -956,42 +953,42 @@
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
       <c r="V12" s="30"/>
-      <c r="W12" s="30"/>
-      <c r="X12" s="30"/>
-      <c r="Y12" s="30"/>
-      <c r="Z12" s="30"/>
-      <c r="AA12" s="30"/>
-      <c r="AB12" s="30"/>
-      <c r="AC12" s="30"/>
-      <c r="AD12" s="30"/>
-      <c r="AE12" s="30"/>
-      <c r="AF12" s="30"/>
-      <c r="AG12" s="30"/>
-      <c r="AH12" s="30"/>
-      <c r="AI12" s="30"/>
-      <c r="AJ12" s="30"/>
-      <c r="AK12" s="30"/>
-      <c r="AL12" s="30"/>
-      <c r="AM12" s="30"/>
-      <c r="AN12" s="30"/>
-      <c r="AO12" s="30"/>
-      <c r="AP12" s="30"/>
-      <c r="AQ12" s="30"/>
-      <c r="AR12" s="30"/>
-      <c r="AS12" s="30"/>
-      <c r="AT12" s="30"/>
-      <c r="AU12" s="30"/>
-      <c r="AV12" s="30"/>
-      <c r="AW12" s="30"/>
-      <c r="AX12" s="30"/>
-      <c r="AY12" s="30"/>
-      <c r="AZ12" s="30"/>
-      <c r="BA12" s="30"/>
-      <c r="BB12" s="30"/>
-      <c r="BC12" s="30"/>
-      <c r="BD12" s="30"/>
-      <c r="BE12" s="30"/>
-      <c r="BF12" s="30"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="31"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="31"/>
+      <c r="AB12" s="31"/>
+      <c r="AC12" s="31"/>
+      <c r="AD12" s="31"/>
+      <c r="AE12" s="31"/>
+      <c r="AF12" s="31"/>
+      <c r="AG12" s="31"/>
+      <c r="AH12" s="31"/>
+      <c r="AI12" s="31"/>
+      <c r="AJ12" s="31"/>
+      <c r="AK12" s="31"/>
+      <c r="AL12" s="31"/>
+      <c r="AM12" s="31"/>
+      <c r="AN12" s="31"/>
+      <c r="AO12" s="31"/>
+      <c r="AP12" s="31"/>
+      <c r="AQ12" s="31"/>
+      <c r="AR12" s="31"/>
+      <c r="AS12" s="31"/>
+      <c r="AT12" s="31"/>
+      <c r="AU12" s="31"/>
+      <c r="AV12" s="31"/>
+      <c r="AW12" s="31"/>
+      <c r="AX12" s="31"/>
+      <c r="AY12" s="31"/>
+      <c r="AZ12" s="31"/>
+      <c r="BA12" s="31"/>
+      <c r="BB12" s="31"/>
+      <c r="BC12" s="31"/>
+      <c r="BD12" s="31"/>
+      <c r="BE12" s="31"/>
+      <c r="BF12" s="31"/>
       <c r="BG12" s="3" t="s">
         <v>1</v>
       </c>
@@ -1077,20 +1074,20 @@
       <c r="BQ13" s="5"/>
     </row>
     <row r="14" spans="2:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="23"/>
-      <c r="K14" s="23"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
-      <c r="O14" s="23"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="31"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31"/>
       <c r="P14" s="2" t="s">
         <v>2</v>
       </c>
@@ -1103,19 +1100,19 @@
       <c r="W14" s="2"/>
       <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
-      <c r="Z14" s="23"/>
-      <c r="AA14" s="23"/>
-      <c r="AB14" s="23"/>
-      <c r="AC14" s="23"/>
-      <c r="AD14" s="23"/>
-      <c r="AE14" s="23"/>
-      <c r="AF14" s="23"/>
-      <c r="AG14" s="23"/>
-      <c r="AH14" s="23"/>
-      <c r="AI14" s="23"/>
-      <c r="AJ14" s="23"/>
-      <c r="AK14" s="23"/>
-      <c r="AL14" s="23"/>
+      <c r="Z14" s="31"/>
+      <c r="AA14" s="31"/>
+      <c r="AB14" s="31"/>
+      <c r="AC14" s="31"/>
+      <c r="AD14" s="31"/>
+      <c r="AE14" s="31"/>
+      <c r="AF14" s="31"/>
+      <c r="AG14" s="31"/>
+      <c r="AH14" s="31"/>
+      <c r="AI14" s="31"/>
+      <c r="AJ14" s="31"/>
+      <c r="AK14" s="31"/>
+      <c r="AL14" s="31"/>
       <c r="AM14" s="5" t="s">
         <v>3</v>
       </c>
@@ -1363,73 +1360,73 @@
       <c r="BQ17" s="6"/>
     </row>
     <row r="18" spans="2:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="30"/>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="30"/>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="30"/>
-      <c r="R18" s="30"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="30"/>
-      <c r="U18" s="30"/>
-      <c r="V18" s="30"/>
-      <c r="W18" s="30"/>
-      <c r="X18" s="30"/>
-      <c r="Y18" s="30"/>
-      <c r="Z18" s="30"/>
-      <c r="AA18" s="30"/>
-      <c r="AB18" s="30"/>
-      <c r="AC18" s="30"/>
-      <c r="AD18" s="30"/>
-      <c r="AE18" s="30"/>
-      <c r="AF18" s="30"/>
-      <c r="AG18" s="30"/>
-      <c r="AH18" s="30"/>
-      <c r="AI18" s="30"/>
-      <c r="AJ18" s="30"/>
-      <c r="AK18" s="30"/>
-      <c r="AL18" s="30"/>
-      <c r="AM18" s="30"/>
-      <c r="AN18" s="30"/>
-      <c r="AO18" s="30"/>
-      <c r="AP18" s="30"/>
-      <c r="AQ18" s="30"/>
-      <c r="AR18" s="30"/>
-      <c r="AS18" s="30"/>
-      <c r="AT18" s="30"/>
-      <c r="AU18" s="30"/>
-      <c r="AV18" s="30"/>
-      <c r="AW18" s="30"/>
-      <c r="AX18" s="30"/>
-      <c r="AY18" s="30"/>
-      <c r="AZ18" s="30"/>
-      <c r="BA18" s="30"/>
-      <c r="BB18" s="30"/>
-      <c r="BC18" s="30"/>
-      <c r="BD18" s="30"/>
-      <c r="BE18" s="30"/>
-      <c r="BF18" s="30"/>
-      <c r="BG18" s="30"/>
-      <c r="BH18" s="30"/>
-      <c r="BI18" s="30"/>
-      <c r="BJ18" s="30"/>
-      <c r="BK18" s="30"/>
-      <c r="BL18" s="30"/>
-      <c r="BM18" s="30"/>
-      <c r="BN18" s="30"/>
-      <c r="BO18" s="30"/>
-      <c r="BP18" s="32"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="32"/>
+      <c r="N18" s="32"/>
+      <c r="O18" s="32"/>
+      <c r="P18" s="32"/>
+      <c r="Q18" s="32"/>
+      <c r="R18" s="32"/>
+      <c r="S18" s="32"/>
+      <c r="T18" s="32"/>
+      <c r="U18" s="32"/>
+      <c r="V18" s="32"/>
+      <c r="W18" s="32"/>
+      <c r="X18" s="32"/>
+      <c r="Y18" s="32"/>
+      <c r="Z18" s="32"/>
+      <c r="AA18" s="32"/>
+      <c r="AB18" s="32"/>
+      <c r="AC18" s="32"/>
+      <c r="AD18" s="32"/>
+      <c r="AE18" s="32"/>
+      <c r="AF18" s="32"/>
+      <c r="AG18" s="32"/>
+      <c r="AH18" s="32"/>
+      <c r="AI18" s="32"/>
+      <c r="AJ18" s="32"/>
+      <c r="AK18" s="32"/>
+      <c r="AL18" s="32"/>
+      <c r="AM18" s="32"/>
+      <c r="AN18" s="32"/>
+      <c r="AO18" s="32"/>
+      <c r="AP18" s="32"/>
+      <c r="AQ18" s="32"/>
+      <c r="AR18" s="32"/>
+      <c r="AS18" s="32"/>
+      <c r="AT18" s="32"/>
+      <c r="AU18" s="32"/>
+      <c r="AV18" s="32"/>
+      <c r="AW18" s="32"/>
+      <c r="AX18" s="32"/>
+      <c r="AY18" s="32"/>
+      <c r="AZ18" s="32"/>
+      <c r="BA18" s="32"/>
+      <c r="BB18" s="32"/>
+      <c r="BC18" s="32"/>
+      <c r="BD18" s="32"/>
+      <c r="BE18" s="32"/>
+      <c r="BF18" s="32"/>
+      <c r="BG18" s="32"/>
+      <c r="BH18" s="32"/>
+      <c r="BI18" s="32"/>
+      <c r="BJ18" s="32"/>
+      <c r="BK18" s="32"/>
+      <c r="BL18" s="32"/>
+      <c r="BM18" s="32"/>
+      <c r="BN18" s="32"/>
+      <c r="BO18" s="32"/>
+      <c r="BP18" s="29"/>
       <c r="BQ18" s="6"/>
     </row>
     <row r="19" spans="2:69" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1503,73 +1500,73 @@
       <c r="BQ19" s="6"/>
     </row>
     <row r="20" spans="2:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="30"/>
-      <c r="AA20" s="30"/>
-      <c r="AB20" s="30"/>
-      <c r="AC20" s="30"/>
-      <c r="AD20" s="30"/>
-      <c r="AE20" s="30"/>
-      <c r="AF20" s="30"/>
-      <c r="AG20" s="30"/>
-      <c r="AH20" s="30"/>
-      <c r="AI20" s="30"/>
-      <c r="AJ20" s="30"/>
-      <c r="AK20" s="30"/>
-      <c r="AL20" s="30"/>
-      <c r="AM20" s="30"/>
-      <c r="AN20" s="30"/>
-      <c r="AO20" s="30"/>
-      <c r="AP20" s="30"/>
-      <c r="AQ20" s="30"/>
-      <c r="AR20" s="30"/>
-      <c r="AS20" s="30"/>
-      <c r="AT20" s="30"/>
-      <c r="AU20" s="30"/>
-      <c r="AV20" s="30"/>
-      <c r="AW20" s="30"/>
-      <c r="AX20" s="30"/>
-      <c r="AY20" s="30"/>
-      <c r="AZ20" s="30"/>
-      <c r="BA20" s="30"/>
-      <c r="BB20" s="30"/>
-      <c r="BC20" s="30"/>
-      <c r="BD20" s="30"/>
-      <c r="BE20" s="30"/>
-      <c r="BF20" s="30"/>
-      <c r="BG20" s="30"/>
-      <c r="BH20" s="30"/>
-      <c r="BI20" s="30"/>
-      <c r="BJ20" s="30"/>
-      <c r="BK20" s="30"/>
-      <c r="BL20" s="30"/>
-      <c r="BM20" s="30"/>
-      <c r="BN20" s="30"/>
-      <c r="BO20" s="30"/>
-      <c r="BP20" s="32"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="32"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="32"/>
+      <c r="Y20" s="32"/>
+      <c r="Z20" s="32"/>
+      <c r="AA20" s="32"/>
+      <c r="AB20" s="32"/>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="32"/>
+      <c r="AE20" s="32"/>
+      <c r="AF20" s="32"/>
+      <c r="AG20" s="32"/>
+      <c r="AH20" s="32"/>
+      <c r="AI20" s="32"/>
+      <c r="AJ20" s="32"/>
+      <c r="AK20" s="32"/>
+      <c r="AL20" s="32"/>
+      <c r="AM20" s="32"/>
+      <c r="AN20" s="32"/>
+      <c r="AO20" s="32"/>
+      <c r="AP20" s="32"/>
+      <c r="AQ20" s="32"/>
+      <c r="AR20" s="32"/>
+      <c r="AS20" s="32"/>
+      <c r="AT20" s="32"/>
+      <c r="AU20" s="32"/>
+      <c r="AV20" s="32"/>
+      <c r="AW20" s="32"/>
+      <c r="AX20" s="32"/>
+      <c r="AY20" s="32"/>
+      <c r="AZ20" s="32"/>
+      <c r="BA20" s="32"/>
+      <c r="BB20" s="32"/>
+      <c r="BC20" s="32"/>
+      <c r="BD20" s="32"/>
+      <c r="BE20" s="32"/>
+      <c r="BF20" s="32"/>
+      <c r="BG20" s="32"/>
+      <c r="BH20" s="32"/>
+      <c r="BI20" s="32"/>
+      <c r="BJ20" s="32"/>
+      <c r="BK20" s="32"/>
+      <c r="BL20" s="32"/>
+      <c r="BM20" s="32"/>
+      <c r="BN20" s="32"/>
+      <c r="BO20" s="32"/>
+      <c r="BP20" s="29"/>
       <c r="BQ20" s="6"/>
     </row>
     <row r="21" spans="2:69" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1643,73 +1640,73 @@
       <c r="BQ21" s="1"/>
     </row>
     <row r="22" spans="2:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
-      <c r="E22" s="30"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="30"/>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="30"/>
-      <c r="L22" s="30"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="30"/>
-      <c r="O22" s="30"/>
-      <c r="P22" s="30"/>
-      <c r="Q22" s="30"/>
-      <c r="R22" s="30"/>
-      <c r="S22" s="30"/>
-      <c r="T22" s="30"/>
-      <c r="U22" s="30"/>
-      <c r="V22" s="30"/>
-      <c r="W22" s="30"/>
-      <c r="X22" s="30"/>
-      <c r="Y22" s="30"/>
-      <c r="Z22" s="30"/>
-      <c r="AA22" s="30"/>
-      <c r="AB22" s="30"/>
-      <c r="AC22" s="30"/>
-      <c r="AD22" s="30"/>
-      <c r="AE22" s="30"/>
-      <c r="AF22" s="30"/>
-      <c r="AG22" s="30"/>
-      <c r="AH22" s="30"/>
-      <c r="AI22" s="30"/>
-      <c r="AJ22" s="30"/>
-      <c r="AK22" s="30"/>
-      <c r="AL22" s="30"/>
-      <c r="AM22" s="30"/>
-      <c r="AN22" s="30"/>
-      <c r="AO22" s="30"/>
-      <c r="AP22" s="30"/>
-      <c r="AQ22" s="30"/>
-      <c r="AR22" s="30"/>
-      <c r="AS22" s="30"/>
-      <c r="AT22" s="30"/>
-      <c r="AU22" s="30"/>
-      <c r="AV22" s="30"/>
-      <c r="AW22" s="30"/>
-      <c r="AX22" s="30"/>
-      <c r="AY22" s="30"/>
-      <c r="AZ22" s="30"/>
-      <c r="BA22" s="30"/>
-      <c r="BB22" s="30"/>
-      <c r="BC22" s="30"/>
-      <c r="BD22" s="30"/>
-      <c r="BE22" s="30"/>
-      <c r="BF22" s="30"/>
-      <c r="BG22" s="30"/>
-      <c r="BH22" s="30"/>
-      <c r="BI22" s="30"/>
-      <c r="BJ22" s="30"/>
-      <c r="BK22" s="30"/>
-      <c r="BL22" s="30"/>
-      <c r="BM22" s="30"/>
-      <c r="BN22" s="30"/>
-      <c r="BO22" s="30"/>
-      <c r="BP22" s="32"/>
+      <c r="B22" s="32"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="32"/>
+      <c r="P22" s="32"/>
+      <c r="Q22" s="32"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="32"/>
+      <c r="U22" s="32"/>
+      <c r="V22" s="32"/>
+      <c r="W22" s="32"/>
+      <c r="X22" s="32"/>
+      <c r="Y22" s="32"/>
+      <c r="Z22" s="32"/>
+      <c r="AA22" s="32"/>
+      <c r="AB22" s="32"/>
+      <c r="AC22" s="32"/>
+      <c r="AD22" s="32"/>
+      <c r="AE22" s="32"/>
+      <c r="AF22" s="32"/>
+      <c r="AG22" s="32"/>
+      <c r="AH22" s="32"/>
+      <c r="AI22" s="32"/>
+      <c r="AJ22" s="32"/>
+      <c r="AK22" s="32"/>
+      <c r="AL22" s="32"/>
+      <c r="AM22" s="32"/>
+      <c r="AN22" s="32"/>
+      <c r="AO22" s="32"/>
+      <c r="AP22" s="32"/>
+      <c r="AQ22" s="32"/>
+      <c r="AR22" s="32"/>
+      <c r="AS22" s="32"/>
+      <c r="AT22" s="32"/>
+      <c r="AU22" s="32"/>
+      <c r="AV22" s="32"/>
+      <c r="AW22" s="32"/>
+      <c r="AX22" s="32"/>
+      <c r="AY22" s="32"/>
+      <c r="AZ22" s="32"/>
+      <c r="BA22" s="32"/>
+      <c r="BB22" s="32"/>
+      <c r="BC22" s="32"/>
+      <c r="BD22" s="32"/>
+      <c r="BE22" s="32"/>
+      <c r="BF22" s="32"/>
+      <c r="BG22" s="32"/>
+      <c r="BH22" s="32"/>
+      <c r="BI22" s="32"/>
+      <c r="BJ22" s="32"/>
+      <c r="BK22" s="32"/>
+      <c r="BL22" s="32"/>
+      <c r="BM22" s="32"/>
+      <c r="BN22" s="32"/>
+      <c r="BO22" s="32"/>
+      <c r="BP22" s="29"/>
       <c r="BQ22" s="1"/>
     </row>
     <row r="23" spans="2:69" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1783,73 +1780,73 @@
       <c r="BQ23" s="1"/>
     </row>
     <row r="24" spans="2:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
-      <c r="P24" s="30"/>
-      <c r="Q24" s="30"/>
-      <c r="R24" s="30"/>
-      <c r="S24" s="30"/>
-      <c r="T24" s="30"/>
-      <c r="U24" s="30"/>
-      <c r="V24" s="30"/>
-      <c r="W24" s="30"/>
-      <c r="X24" s="30"/>
-      <c r="Y24" s="30"/>
-      <c r="Z24" s="30"/>
-      <c r="AA24" s="30"/>
-      <c r="AB24" s="30"/>
-      <c r="AC24" s="30"/>
-      <c r="AD24" s="30"/>
-      <c r="AE24" s="30"/>
-      <c r="AF24" s="30"/>
-      <c r="AG24" s="30"/>
-      <c r="AH24" s="30"/>
-      <c r="AI24" s="30"/>
-      <c r="AJ24" s="30"/>
-      <c r="AK24" s="30"/>
-      <c r="AL24" s="30"/>
-      <c r="AM24" s="30"/>
-      <c r="AN24" s="30"/>
-      <c r="AO24" s="30"/>
-      <c r="AP24" s="30"/>
-      <c r="AQ24" s="30"/>
-      <c r="AR24" s="30"/>
-      <c r="AS24" s="30"/>
-      <c r="AT24" s="30"/>
-      <c r="AU24" s="30"/>
-      <c r="AV24" s="30"/>
-      <c r="AW24" s="30"/>
-      <c r="AX24" s="30"/>
-      <c r="AY24" s="30"/>
-      <c r="AZ24" s="30"/>
-      <c r="BA24" s="30"/>
-      <c r="BB24" s="30"/>
-      <c r="BC24" s="30"/>
-      <c r="BD24" s="30"/>
-      <c r="BE24" s="30"/>
-      <c r="BF24" s="30"/>
-      <c r="BG24" s="30"/>
-      <c r="BH24" s="30"/>
-      <c r="BI24" s="30"/>
-      <c r="BJ24" s="30"/>
-      <c r="BK24" s="30"/>
-      <c r="BL24" s="30"/>
-      <c r="BM24" s="30"/>
-      <c r="BN24" s="30"/>
-      <c r="BO24" s="30"/>
-      <c r="BP24" s="32"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="32"/>
+      <c r="O24" s="32"/>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="32"/>
+      <c r="R24" s="32"/>
+      <c r="S24" s="32"/>
+      <c r="T24" s="32"/>
+      <c r="U24" s="32"/>
+      <c r="V24" s="32"/>
+      <c r="W24" s="32"/>
+      <c r="X24" s="32"/>
+      <c r="Y24" s="32"/>
+      <c r="Z24" s="32"/>
+      <c r="AA24" s="32"/>
+      <c r="AB24" s="32"/>
+      <c r="AC24" s="32"/>
+      <c r="AD24" s="32"/>
+      <c r="AE24" s="32"/>
+      <c r="AF24" s="32"/>
+      <c r="AG24" s="32"/>
+      <c r="AH24" s="32"/>
+      <c r="AI24" s="32"/>
+      <c r="AJ24" s="32"/>
+      <c r="AK24" s="32"/>
+      <c r="AL24" s="32"/>
+      <c r="AM24" s="32"/>
+      <c r="AN24" s="32"/>
+      <c r="AO24" s="32"/>
+      <c r="AP24" s="32"/>
+      <c r="AQ24" s="32"/>
+      <c r="AR24" s="32"/>
+      <c r="AS24" s="32"/>
+      <c r="AT24" s="32"/>
+      <c r="AU24" s="32"/>
+      <c r="AV24" s="32"/>
+      <c r="AW24" s="32"/>
+      <c r="AX24" s="32"/>
+      <c r="AY24" s="32"/>
+      <c r="AZ24" s="32"/>
+      <c r="BA24" s="32"/>
+      <c r="BB24" s="32"/>
+      <c r="BC24" s="32"/>
+      <c r="BD24" s="32"/>
+      <c r="BE24" s="32"/>
+      <c r="BF24" s="32"/>
+      <c r="BG24" s="32"/>
+      <c r="BH24" s="32"/>
+      <c r="BI24" s="32"/>
+      <c r="BJ24" s="32"/>
+      <c r="BK24" s="32"/>
+      <c r="BL24" s="32"/>
+      <c r="BM24" s="32"/>
+      <c r="BN24" s="32"/>
+      <c r="BO24" s="32"/>
+      <c r="BP24" s="29"/>
     </row>
     <row r="25" spans="2:69" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="1"/>
@@ -1876,19 +1873,19 @@
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
-      <c r="P26" s="33"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="23"/>
-      <c r="S26" s="23"/>
-      <c r="T26" s="23"/>
-      <c r="U26" s="23"/>
-      <c r="V26" s="23"/>
-      <c r="W26" s="23"/>
-      <c r="X26" s="23"/>
-      <c r="Y26" s="23"/>
-      <c r="Z26" s="23"/>
-      <c r="AA26" s="23"/>
-      <c r="AB26" s="22"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="31"/>
+      <c r="Z26" s="31"/>
+      <c r="AA26" s="31"/>
+      <c r="AB26" s="21"/>
       <c r="AC26" s="2" t="s">
         <v>5</v>
       </c>
@@ -1910,20 +1907,20 @@
       <c r="AS26" s="2"/>
       <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
-      <c r="AV26" s="23"/>
-      <c r="AW26" s="23"/>
-      <c r="AX26" s="23"/>
-      <c r="AY26" s="23"/>
-      <c r="AZ26" s="23"/>
-      <c r="BA26" s="23"/>
-      <c r="BB26" s="23"/>
-      <c r="BC26" s="23"/>
-      <c r="BD26" s="23"/>
-      <c r="BE26" s="23"/>
-      <c r="BF26" s="22"/>
-      <c r="BG26" s="22"/>
-      <c r="BH26" s="22"/>
-      <c r="BI26" s="22"/>
+      <c r="AV26" s="31"/>
+      <c r="AW26" s="31"/>
+      <c r="AX26" s="31"/>
+      <c r="AY26" s="31"/>
+      <c r="AZ26" s="31"/>
+      <c r="BA26" s="31"/>
+      <c r="BB26" s="31"/>
+      <c r="BC26" s="31"/>
+      <c r="BD26" s="31"/>
+      <c r="BE26" s="31"/>
+      <c r="BF26" s="21"/>
+      <c r="BG26" s="21"/>
+      <c r="BH26" s="21"/>
+      <c r="BI26" s="21"/>
     </row>
     <row r="27" spans="2:69" ht="1.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="1"/>
@@ -1976,18 +1973,18 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="7"/>
-      <c r="O32" s="7"/>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="7"/>
-      <c r="R32" s="7"/>
-      <c r="S32" s="7"/>
-      <c r="T32" s="7"/>
-      <c r="U32" s="7"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="31"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="31"/>
     </row>
     <row r="33" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
@@ -1998,140 +1995,140 @@
       <c r="G33" s="1"/>
     </row>
     <row r="34" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="M34" s="14" t="s">
+      <c r="M34" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="N34" s="15"/>
-      <c r="O34" s="15"/>
-      <c r="P34" s="15"/>
-      <c r="Q34" s="15"/>
-      <c r="R34" s="15"/>
-      <c r="S34" s="15"/>
-      <c r="T34" s="15"/>
-      <c r="U34" s="15"/>
-      <c r="V34" s="15"/>
-      <c r="W34" s="15"/>
-      <c r="X34" s="15"/>
-      <c r="Y34" s="15"/>
-      <c r="Z34" s="15"/>
-      <c r="AA34" s="15"/>
-      <c r="AB34" s="16"/>
-      <c r="AP34" s="14" t="s">
+      <c r="N34" s="14"/>
+      <c r="O34" s="14"/>
+      <c r="P34" s="14"/>
+      <c r="Q34" s="14"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="14"/>
+      <c r="T34" s="14"/>
+      <c r="U34" s="14"/>
+      <c r="V34" s="14"/>
+      <c r="W34" s="14"/>
+      <c r="X34" s="14"/>
+      <c r="Y34" s="14"/>
+      <c r="Z34" s="14"/>
+      <c r="AA34" s="14"/>
+      <c r="AB34" s="15"/>
+      <c r="AP34" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AQ34" s="15"/>
-      <c r="AR34" s="15"/>
-      <c r="AS34" s="15"/>
-      <c r="AT34" s="15"/>
-      <c r="AU34" s="15"/>
-      <c r="AV34" s="15"/>
-      <c r="AW34" s="15"/>
-      <c r="AX34" s="15"/>
-      <c r="AY34" s="15"/>
-      <c r="AZ34" s="15"/>
-      <c r="BA34" s="15"/>
-      <c r="BB34" s="15"/>
-      <c r="BC34" s="15"/>
-      <c r="BD34" s="16"/>
+      <c r="AQ34" s="14"/>
+      <c r="AR34" s="14"/>
+      <c r="AS34" s="14"/>
+      <c r="AT34" s="14"/>
+      <c r="AU34" s="14"/>
+      <c r="AV34" s="14"/>
+      <c r="AW34" s="14"/>
+      <c r="AX34" s="14"/>
+      <c r="AY34" s="14"/>
+      <c r="AZ34" s="14"/>
+      <c r="BA34" s="14"/>
+      <c r="BB34" s="14"/>
+      <c r="BC34" s="14"/>
+      <c r="BD34" s="15"/>
     </row>
     <row r="35" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="M35" s="24"/>
-      <c r="N35" s="25"/>
-      <c r="O35" s="9"/>
-      <c r="P35" s="9"/>
-      <c r="Q35" s="9"/>
-      <c r="R35" s="9"/>
-      <c r="S35" s="9"/>
-      <c r="T35" s="9"/>
-      <c r="U35" s="9"/>
-      <c r="V35" s="9"/>
-      <c r="W35" s="9"/>
-      <c r="X35" s="9"/>
-      <c r="Y35" s="9"/>
-      <c r="Z35" s="9"/>
-      <c r="AA35" s="9"/>
-      <c r="AB35" s="10"/>
-      <c r="AP35" s="8"/>
-      <c r="AQ35" s="9"/>
-      <c r="AR35" s="9"/>
-      <c r="AS35" s="9"/>
-      <c r="AT35" s="9"/>
-      <c r="AU35" s="9"/>
-      <c r="AV35" s="9"/>
-      <c r="AW35" s="9"/>
-      <c r="AX35" s="9"/>
-      <c r="AY35" s="9"/>
-      <c r="AZ35" s="9"/>
-      <c r="BA35" s="9"/>
-      <c r="BB35" s="9"/>
-      <c r="BC35" s="9"/>
-      <c r="BD35" s="28"/>
+      <c r="M35" s="22"/>
+      <c r="N35" s="23"/>
+      <c r="O35" s="8"/>
+      <c r="P35" s="8"/>
+      <c r="Q35" s="8"/>
+      <c r="R35" s="8"/>
+      <c r="S35" s="8"/>
+      <c r="T35" s="8"/>
+      <c r="U35" s="8"/>
+      <c r="V35" s="8"/>
+      <c r="W35" s="8"/>
+      <c r="X35" s="8"/>
+      <c r="Y35" s="8"/>
+      <c r="Z35" s="8"/>
+      <c r="AA35" s="8"/>
+      <c r="AB35" s="9"/>
+      <c r="AP35" s="7"/>
+      <c r="AQ35" s="8"/>
+      <c r="AR35" s="8"/>
+      <c r="AS35" s="8"/>
+      <c r="AT35" s="8"/>
+      <c r="AU35" s="8"/>
+      <c r="AV35" s="8"/>
+      <c r="AW35" s="8"/>
+      <c r="AX35" s="8"/>
+      <c r="AY35" s="8"/>
+      <c r="AZ35" s="8"/>
+      <c r="BA35" s="8"/>
+      <c r="BB35" s="8"/>
+      <c r="BC35" s="8"/>
+      <c r="BD35" s="26"/>
     </row>
     <row r="36" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="M36" s="24"/>
-      <c r="N36" s="25"/>
-      <c r="O36" s="9"/>
-      <c r="P36" s="9"/>
-      <c r="Q36" s="9"/>
-      <c r="R36" s="9"/>
-      <c r="S36" s="9"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="10"/>
-      <c r="AP36" s="8"/>
-      <c r="AQ36" s="9"/>
-      <c r="AR36" s="9"/>
-      <c r="AS36" s="9"/>
-      <c r="AT36" s="9"/>
-      <c r="AU36" s="9"/>
-      <c r="AV36" s="9"/>
-      <c r="AW36" s="9"/>
-      <c r="AX36" s="9"/>
-      <c r="AY36" s="9"/>
-      <c r="AZ36" s="9"/>
-      <c r="BA36" s="9"/>
-      <c r="BB36" s="9"/>
-      <c r="BC36" s="9"/>
-      <c r="BD36" s="28"/>
+      <c r="M36" s="22"/>
+      <c r="N36" s="23"/>
+      <c r="O36" s="8"/>
+      <c r="P36" s="8"/>
+      <c r="Q36" s="8"/>
+      <c r="R36" s="8"/>
+      <c r="S36" s="8"/>
+      <c r="T36" s="8"/>
+      <c r="U36" s="8"/>
+      <c r="V36" s="8"/>
+      <c r="W36" s="8"/>
+      <c r="X36" s="8"/>
+      <c r="Y36" s="8"/>
+      <c r="Z36" s="8"/>
+      <c r="AA36" s="8"/>
+      <c r="AB36" s="9"/>
+      <c r="AP36" s="7"/>
+      <c r="AQ36" s="8"/>
+      <c r="AR36" s="8"/>
+      <c r="AS36" s="8"/>
+      <c r="AT36" s="8"/>
+      <c r="AU36" s="8"/>
+      <c r="AV36" s="8"/>
+      <c r="AW36" s="8"/>
+      <c r="AX36" s="8"/>
+      <c r="AY36" s="8"/>
+      <c r="AZ36" s="8"/>
+      <c r="BA36" s="8"/>
+      <c r="BB36" s="8"/>
+      <c r="BC36" s="8"/>
+      <c r="BD36" s="26"/>
     </row>
     <row r="37" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="M37" s="26"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="12"/>
-      <c r="P37" s="12"/>
-      <c r="Q37" s="12"/>
-      <c r="R37" s="12"/>
-      <c r="S37" s="12"/>
-      <c r="T37" s="12"/>
-      <c r="U37" s="12"/>
-      <c r="V37" s="12"/>
-      <c r="W37" s="12"/>
-      <c r="X37" s="12"/>
-      <c r="Y37" s="12"/>
-      <c r="Z37" s="12"/>
-      <c r="AA37" s="12"/>
-      <c r="AB37" s="13"/>
-      <c r="AP37" s="11"/>
-      <c r="AQ37" s="12"/>
-      <c r="AR37" s="12"/>
-      <c r="AS37" s="12"/>
-      <c r="AT37" s="12"/>
-      <c r="AU37" s="12"/>
-      <c r="AV37" s="12"/>
-      <c r="AW37" s="12"/>
-      <c r="AX37" s="12"/>
-      <c r="AY37" s="12"/>
-      <c r="AZ37" s="12"/>
-      <c r="BA37" s="12"/>
-      <c r="BB37" s="12"/>
-      <c r="BC37" s="12"/>
-      <c r="BD37" s="29"/>
+      <c r="M37" s="24"/>
+      <c r="N37" s="25"/>
+      <c r="O37" s="11"/>
+      <c r="P37" s="11"/>
+      <c r="Q37" s="11"/>
+      <c r="R37" s="11"/>
+      <c r="S37" s="11"/>
+      <c r="T37" s="11"/>
+      <c r="U37" s="11"/>
+      <c r="V37" s="11"/>
+      <c r="W37" s="11"/>
+      <c r="X37" s="11"/>
+      <c r="Y37" s="11"/>
+      <c r="Z37" s="11"/>
+      <c r="AA37" s="11"/>
+      <c r="AB37" s="12"/>
+      <c r="AP37" s="10"/>
+      <c r="AQ37" s="11"/>
+      <c r="AR37" s="11"/>
+      <c r="AS37" s="11"/>
+      <c r="AT37" s="11"/>
+      <c r="AU37" s="11"/>
+      <c r="AV37" s="11"/>
+      <c r="AW37" s="11"/>
+      <c r="AX37" s="11"/>
+      <c r="AY37" s="11"/>
+      <c r="AZ37" s="11"/>
+      <c r="BA37" s="11"/>
+      <c r="BB37" s="11"/>
+      <c r="BC37" s="11"/>
+      <c r="BD37" s="27"/>
     </row>
     <row r="38" spans="2:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="2:56" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2149,303 +2146,304 @@
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
-      <c r="L42" s="23"/>
-      <c r="M42" s="23"/>
-      <c r="N42" s="23"/>
-      <c r="O42" s="23"/>
-      <c r="P42" s="23"/>
-      <c r="Q42" s="23"/>
-      <c r="R42" s="23"/>
-      <c r="S42" s="23"/>
-      <c r="T42" s="23"/>
-      <c r="U42" s="23"/>
-      <c r="V42" s="23"/>
-      <c r="W42" s="23"/>
+      <c r="L42" s="31"/>
+      <c r="M42" s="31"/>
+      <c r="N42" s="31"/>
+      <c r="O42" s="31"/>
+      <c r="P42" s="31"/>
+      <c r="Q42" s="31"/>
+      <c r="R42" s="31"/>
+      <c r="S42" s="31"/>
+      <c r="T42" s="31"/>
+      <c r="U42" s="31"/>
+      <c r="V42" s="31"/>
+      <c r="W42" s="31"/>
     </row>
     <row r="44" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="M44" s="14" t="s">
+      <c r="M44" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="N44" s="15"/>
-      <c r="O44" s="15"/>
-      <c r="P44" s="15"/>
-      <c r="Q44" s="15"/>
-      <c r="R44" s="15"/>
-      <c r="S44" s="15"/>
-      <c r="T44" s="15"/>
-      <c r="U44" s="15"/>
-      <c r="V44" s="15"/>
-      <c r="W44" s="15"/>
-      <c r="X44" s="15"/>
-      <c r="Y44" s="15"/>
-      <c r="Z44" s="15"/>
-      <c r="AA44" s="15"/>
-      <c r="AB44" s="16"/>
-      <c r="AP44" s="14" t="s">
+      <c r="N44" s="14"/>
+      <c r="O44" s="14"/>
+      <c r="P44" s="14"/>
+      <c r="Q44" s="14"/>
+      <c r="R44" s="14"/>
+      <c r="S44" s="14"/>
+      <c r="T44" s="14"/>
+      <c r="U44" s="14"/>
+      <c r="V44" s="14"/>
+      <c r="W44" s="14"/>
+      <c r="X44" s="14"/>
+      <c r="Y44" s="14"/>
+      <c r="Z44" s="14"/>
+      <c r="AA44" s="14"/>
+      <c r="AB44" s="15"/>
+      <c r="AP44" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AQ44" s="15"/>
-      <c r="AR44" s="15"/>
-      <c r="AS44" s="15"/>
-      <c r="AT44" s="15"/>
-      <c r="AU44" s="15"/>
-      <c r="AV44" s="15"/>
-      <c r="AW44" s="15"/>
-      <c r="AX44" s="15"/>
-      <c r="AY44" s="15"/>
-      <c r="AZ44" s="15"/>
-      <c r="BA44" s="15"/>
-      <c r="BB44" s="15"/>
-      <c r="BC44" s="15"/>
-      <c r="BD44" s="16"/>
+      <c r="AQ44" s="14"/>
+      <c r="AR44" s="14"/>
+      <c r="AS44" s="14"/>
+      <c r="AT44" s="14"/>
+      <c r="AU44" s="14"/>
+      <c r="AV44" s="14"/>
+      <c r="AW44" s="14"/>
+      <c r="AX44" s="14"/>
+      <c r="AY44" s="14"/>
+      <c r="AZ44" s="14"/>
+      <c r="BA44" s="14"/>
+      <c r="BB44" s="14"/>
+      <c r="BC44" s="14"/>
+      <c r="BD44" s="15"/>
     </row>
     <row r="45" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="M45" s="24"/>
-      <c r="N45" s="25"/>
-      <c r="O45" s="9"/>
-      <c r="P45" s="9"/>
-      <c r="Q45" s="9"/>
-      <c r="R45" s="9"/>
-      <c r="S45" s="9"/>
-      <c r="T45" s="9"/>
-      <c r="U45" s="9"/>
-      <c r="V45" s="9"/>
-      <c r="W45" s="9"/>
-      <c r="X45" s="9"/>
-      <c r="Y45" s="9"/>
-      <c r="Z45" s="9"/>
-      <c r="AA45" s="9"/>
-      <c r="AB45" s="10"/>
-      <c r="AP45" s="8"/>
-      <c r="AQ45" s="9"/>
-      <c r="AR45" s="9"/>
-      <c r="AS45" s="9"/>
-      <c r="AT45" s="9"/>
-      <c r="AU45" s="9"/>
-      <c r="AV45" s="9"/>
-      <c r="AW45" s="9"/>
-      <c r="AX45" s="9"/>
-      <c r="AY45" s="9"/>
-      <c r="AZ45" s="9"/>
-      <c r="BA45" s="9"/>
-      <c r="BB45" s="9"/>
-      <c r="BC45" s="9"/>
-      <c r="BD45" s="28"/>
+      <c r="M45" s="22"/>
+      <c r="N45" s="23"/>
+      <c r="O45" s="8"/>
+      <c r="P45" s="8"/>
+      <c r="Q45" s="8"/>
+      <c r="R45" s="8"/>
+      <c r="S45" s="8"/>
+      <c r="T45" s="8"/>
+      <c r="U45" s="8"/>
+      <c r="V45" s="8"/>
+      <c r="W45" s="8"/>
+      <c r="X45" s="8"/>
+      <c r="Y45" s="8"/>
+      <c r="Z45" s="8"/>
+      <c r="AA45" s="8"/>
+      <c r="AB45" s="9"/>
+      <c r="AP45" s="7"/>
+      <c r="AQ45" s="8"/>
+      <c r="AR45" s="8"/>
+      <c r="AS45" s="8"/>
+      <c r="AT45" s="8"/>
+      <c r="AU45" s="8"/>
+      <c r="AV45" s="8"/>
+      <c r="AW45" s="8"/>
+      <c r="AX45" s="8"/>
+      <c r="AY45" s="8"/>
+      <c r="AZ45" s="8"/>
+      <c r="BA45" s="8"/>
+      <c r="BB45" s="8"/>
+      <c r="BC45" s="8"/>
+      <c r="BD45" s="26"/>
     </row>
     <row r="46" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="M46" s="24"/>
-      <c r="N46" s="25"/>
-      <c r="O46" s="9"/>
-      <c r="P46" s="9"/>
-      <c r="Q46" s="9"/>
-      <c r="R46" s="9"/>
-      <c r="S46" s="9"/>
-      <c r="T46" s="9"/>
-      <c r="U46" s="9"/>
-      <c r="V46" s="9"/>
-      <c r="W46" s="9"/>
-      <c r="X46" s="9"/>
-      <c r="Y46" s="9"/>
-      <c r="Z46" s="9"/>
-      <c r="AA46" s="9"/>
-      <c r="AB46" s="10"/>
-      <c r="AP46" s="8"/>
-      <c r="AQ46" s="9"/>
-      <c r="AR46" s="9"/>
-      <c r="AS46" s="9"/>
-      <c r="AT46" s="9"/>
-      <c r="AU46" s="9"/>
-      <c r="AV46" s="9"/>
-      <c r="AW46" s="9"/>
-      <c r="AX46" s="9"/>
-      <c r="AY46" s="9"/>
-      <c r="AZ46" s="9"/>
-      <c r="BA46" s="9"/>
-      <c r="BB46" s="9"/>
-      <c r="BC46" s="9"/>
-      <c r="BD46" s="28"/>
+      <c r="M46" s="22"/>
+      <c r="N46" s="23"/>
+      <c r="O46" s="8"/>
+      <c r="P46" s="8"/>
+      <c r="Q46" s="8"/>
+      <c r="R46" s="8"/>
+      <c r="S46" s="8"/>
+      <c r="T46" s="8"/>
+      <c r="U46" s="8"/>
+      <c r="V46" s="8"/>
+      <c r="W46" s="8"/>
+      <c r="X46" s="8"/>
+      <c r="Y46" s="8"/>
+      <c r="Z46" s="8"/>
+      <c r="AA46" s="8"/>
+      <c r="AB46" s="9"/>
+      <c r="AP46" s="7"/>
+      <c r="AQ46" s="8"/>
+      <c r="AR46" s="8"/>
+      <c r="AS46" s="8"/>
+      <c r="AT46" s="8"/>
+      <c r="AU46" s="8"/>
+      <c r="AV46" s="8"/>
+      <c r="AW46" s="8"/>
+      <c r="AX46" s="8"/>
+      <c r="AY46" s="8"/>
+      <c r="AZ46" s="8"/>
+      <c r="BA46" s="8"/>
+      <c r="BB46" s="8"/>
+      <c r="BC46" s="8"/>
+      <c r="BD46" s="26"/>
     </row>
     <row r="47" spans="2:56" x14ac:dyDescent="0.25">
-      <c r="M47" s="26"/>
-      <c r="N47" s="27"/>
-      <c r="O47" s="12"/>
-      <c r="P47" s="12"/>
-      <c r="Q47" s="12"/>
-      <c r="R47" s="12"/>
-      <c r="S47" s="12"/>
-      <c r="T47" s="12"/>
-      <c r="U47" s="12"/>
-      <c r="V47" s="12"/>
-      <c r="W47" s="12"/>
-      <c r="X47" s="12"/>
-      <c r="Y47" s="12"/>
-      <c r="Z47" s="12"/>
-      <c r="AA47" s="12"/>
-      <c r="AB47" s="13"/>
-      <c r="AP47" s="11"/>
-      <c r="AQ47" s="12"/>
-      <c r="AR47" s="12"/>
-      <c r="AS47" s="12"/>
-      <c r="AT47" s="12"/>
-      <c r="AU47" s="12"/>
-      <c r="AV47" s="12"/>
-      <c r="AW47" s="12"/>
-      <c r="AX47" s="12"/>
-      <c r="AY47" s="12"/>
-      <c r="AZ47" s="12"/>
-      <c r="BA47" s="12"/>
-      <c r="BB47" s="12"/>
-      <c r="BC47" s="12"/>
-      <c r="BD47" s="29"/>
+      <c r="M47" s="24"/>
+      <c r="N47" s="25"/>
+      <c r="O47" s="11"/>
+      <c r="P47" s="11"/>
+      <c r="Q47" s="11"/>
+      <c r="R47" s="11"/>
+      <c r="S47" s="11"/>
+      <c r="T47" s="11"/>
+      <c r="U47" s="11"/>
+      <c r="V47" s="11"/>
+      <c r="W47" s="11"/>
+      <c r="X47" s="11"/>
+      <c r="Y47" s="11"/>
+      <c r="Z47" s="11"/>
+      <c r="AA47" s="11"/>
+      <c r="AB47" s="12"/>
+      <c r="AP47" s="10"/>
+      <c r="AQ47" s="11"/>
+      <c r="AR47" s="11"/>
+      <c r="AS47" s="11"/>
+      <c r="AT47" s="11"/>
+      <c r="AU47" s="11"/>
+      <c r="AV47" s="11"/>
+      <c r="AW47" s="11"/>
+      <c r="AX47" s="11"/>
+      <c r="AY47" s="11"/>
+      <c r="AZ47" s="11"/>
+      <c r="BA47" s="11"/>
+      <c r="BB47" s="11"/>
+      <c r="BC47" s="11"/>
+      <c r="BD47" s="27"/>
     </row>
     <row r="53" spans="2:68" ht="10.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="54" spans="2:68" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="18" t="s">
+      <c r="B54" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C54" s="18"/>
-      <c r="D54" s="18"/>
-      <c r="E54" s="18"/>
-      <c r="F54" s="18"/>
-      <c r="G54" s="18"/>
-      <c r="H54" s="18"/>
-      <c r="I54" s="18"/>
-      <c r="J54" s="18"/>
-      <c r="K54" s="18"/>
-      <c r="L54" s="18"/>
-      <c r="M54" s="18"/>
-      <c r="N54" s="18"/>
-      <c r="O54" s="18"/>
-      <c r="P54" s="18"/>
-      <c r="Q54" s="18"/>
-      <c r="R54" s="18"/>
-      <c r="S54" s="18"/>
-      <c r="T54" s="18"/>
-      <c r="U54" s="18"/>
-      <c r="V54" s="18"/>
-      <c r="W54" s="18"/>
-      <c r="X54" s="18"/>
-      <c r="Y54" s="18"/>
-      <c r="Z54" s="18"/>
-      <c r="AA54" s="18"/>
-      <c r="AB54" s="18"/>
-      <c r="AC54" s="18"/>
-      <c r="AD54" s="18"/>
-      <c r="AE54" s="18"/>
-      <c r="AF54" s="18"/>
-      <c r="AG54" s="18"/>
-      <c r="AH54" s="18"/>
-      <c r="AI54" s="18"/>
-      <c r="AJ54" s="18"/>
-      <c r="AK54" s="18"/>
-      <c r="AL54" s="18"/>
-      <c r="AM54" s="18"/>
-      <c r="AN54" s="18"/>
-      <c r="AO54" s="18"/>
-      <c r="AP54" s="18"/>
-      <c r="AQ54" s="18"/>
-      <c r="AR54" s="18"/>
-      <c r="AS54" s="18"/>
-      <c r="AT54" s="18"/>
-      <c r="AU54" s="18"/>
-      <c r="AV54" s="18"/>
-      <c r="AW54" s="18"/>
-      <c r="AX54" s="18"/>
-      <c r="AY54" s="18"/>
-      <c r="AZ54" s="18"/>
-      <c r="BA54" s="18"/>
-      <c r="BB54" s="18"/>
-      <c r="BC54" s="18"/>
-      <c r="BD54" s="18"/>
-      <c r="BE54" s="18"/>
-      <c r="BF54" s="18"/>
-      <c r="BG54" s="18"/>
-      <c r="BH54" s="18"/>
-      <c r="BI54" s="18"/>
-      <c r="BJ54" s="18"/>
-      <c r="BK54" s="18"/>
-      <c r="BL54" s="18"/>
-      <c r="BM54" s="18"/>
-      <c r="BN54" s="18"/>
-      <c r="BO54" s="18"/>
-      <c r="BP54" s="20"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="17"/>
+      <c r="P54" s="17"/>
+      <c r="Q54" s="17"/>
+      <c r="R54" s="17"/>
+      <c r="S54" s="17"/>
+      <c r="T54" s="17"/>
+      <c r="U54" s="17"/>
+      <c r="V54" s="17"/>
+      <c r="W54" s="17"/>
+      <c r="X54" s="17"/>
+      <c r="Y54" s="17"/>
+      <c r="Z54" s="17"/>
+      <c r="AA54" s="17"/>
+      <c r="AB54" s="17"/>
+      <c r="AC54" s="17"/>
+      <c r="AD54" s="17"/>
+      <c r="AE54" s="17"/>
+      <c r="AF54" s="17"/>
+      <c r="AG54" s="17"/>
+      <c r="AH54" s="17"/>
+      <c r="AI54" s="17"/>
+      <c r="AJ54" s="17"/>
+      <c r="AK54" s="17"/>
+      <c r="AL54" s="17"/>
+      <c r="AM54" s="17"/>
+      <c r="AN54" s="17"/>
+      <c r="AO54" s="17"/>
+      <c r="AP54" s="17"/>
+      <c r="AQ54" s="17"/>
+      <c r="AR54" s="17"/>
+      <c r="AS54" s="17"/>
+      <c r="AT54" s="17"/>
+      <c r="AU54" s="17"/>
+      <c r="AV54" s="17"/>
+      <c r="AW54" s="17"/>
+      <c r="AX54" s="17"/>
+      <c r="AY54" s="17"/>
+      <c r="AZ54" s="17"/>
+      <c r="BA54" s="17"/>
+      <c r="BB54" s="17"/>
+      <c r="BC54" s="17"/>
+      <c r="BD54" s="17"/>
+      <c r="BE54" s="17"/>
+      <c r="BF54" s="17"/>
+      <c r="BG54" s="17"/>
+      <c r="BH54" s="17"/>
+      <c r="BI54" s="17"/>
+      <c r="BJ54" s="17"/>
+      <c r="BK54" s="17"/>
+      <c r="BL54" s="17"/>
+      <c r="BM54" s="17"/>
+      <c r="BN54" s="17"/>
+      <c r="BO54" s="17"/>
+      <c r="BP54" s="19"/>
     </row>
     <row r="55" spans="2:68" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="19" t="s">
+      <c r="B55" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C55" s="19"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
-      <c r="F55" s="19"/>
-      <c r="G55" s="19"/>
-      <c r="H55" s="19"/>
-      <c r="I55" s="19"/>
-      <c r="J55" s="19"/>
-      <c r="K55" s="19"/>
-      <c r="L55" s="19"/>
-      <c r="M55" s="19"/>
-      <c r="N55" s="19"/>
-      <c r="O55" s="19"/>
-      <c r="P55" s="19"/>
-      <c r="Q55" s="19"/>
-      <c r="R55" s="19"/>
-      <c r="S55" s="19"/>
-      <c r="T55" s="19"/>
-      <c r="U55" s="19"/>
-      <c r="V55" s="19"/>
-      <c r="W55" s="19"/>
-      <c r="X55" s="19"/>
-      <c r="Y55" s="19"/>
-      <c r="Z55" s="19"/>
-      <c r="AA55" s="19"/>
-      <c r="AB55" s="19"/>
-      <c r="AC55" s="19"/>
-      <c r="AD55" s="19"/>
-      <c r="AE55" s="19"/>
-      <c r="AF55" s="19"/>
-      <c r="AG55" s="19"/>
-      <c r="AH55" s="19"/>
-      <c r="AI55" s="19"/>
-      <c r="AJ55" s="19"/>
-      <c r="AK55" s="19"/>
-      <c r="AL55" s="19"/>
-      <c r="AM55" s="19"/>
-      <c r="AN55" s="19"/>
-      <c r="AO55" s="19"/>
-      <c r="AP55" s="19"/>
-      <c r="AQ55" s="19"/>
-      <c r="AR55" s="19"/>
-      <c r="AS55" s="19"/>
-      <c r="AT55" s="19"/>
-      <c r="AU55" s="19"/>
-      <c r="AV55" s="19"/>
-      <c r="AW55" s="19"/>
-      <c r="AX55" s="19"/>
-      <c r="AY55" s="19"/>
-      <c r="AZ55" s="19"/>
-      <c r="BA55" s="19"/>
-      <c r="BB55" s="19"/>
-      <c r="BC55" s="19"/>
-      <c r="BD55" s="19"/>
-      <c r="BE55" s="19"/>
-      <c r="BF55" s="19"/>
-      <c r="BG55" s="19"/>
-      <c r="BH55" s="19"/>
-      <c r="BI55" s="19"/>
-      <c r="BJ55" s="19"/>
-      <c r="BK55" s="19"/>
-      <c r="BL55" s="19"/>
-      <c r="BM55" s="19"/>
-      <c r="BN55" s="19"/>
-      <c r="BO55" s="19"/>
-      <c r="BP55" s="21"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="18"/>
+      <c r="I55" s="18"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="18"/>
+      <c r="M55" s="18"/>
+      <c r="N55" s="18"/>
+      <c r="O55" s="18"/>
+      <c r="P55" s="18"/>
+      <c r="Q55" s="18"/>
+      <c r="R55" s="18"/>
+      <c r="S55" s="18"/>
+      <c r="T55" s="18"/>
+      <c r="U55" s="18"/>
+      <c r="V55" s="18"/>
+      <c r="W55" s="18"/>
+      <c r="X55" s="18"/>
+      <c r="Y55" s="18"/>
+      <c r="Z55" s="18"/>
+      <c r="AA55" s="18"/>
+      <c r="AB55" s="18"/>
+      <c r="AC55" s="18"/>
+      <c r="AD55" s="18"/>
+      <c r="AE55" s="18"/>
+      <c r="AF55" s="18"/>
+      <c r="AG55" s="18"/>
+      <c r="AH55" s="18"/>
+      <c r="AI55" s="18"/>
+      <c r="AJ55" s="18"/>
+      <c r="AK55" s="18"/>
+      <c r="AL55" s="18"/>
+      <c r="AM55" s="18"/>
+      <c r="AN55" s="18"/>
+      <c r="AO55" s="18"/>
+      <c r="AP55" s="18"/>
+      <c r="AQ55" s="18"/>
+      <c r="AR55" s="18"/>
+      <c r="AS55" s="18"/>
+      <c r="AT55" s="18"/>
+      <c r="AU55" s="18"/>
+      <c r="AV55" s="18"/>
+      <c r="AW55" s="18"/>
+      <c r="AX55" s="18"/>
+      <c r="AY55" s="18"/>
+      <c r="AZ55" s="18"/>
+      <c r="BA55" s="18"/>
+      <c r="BB55" s="18"/>
+      <c r="BC55" s="18"/>
+      <c r="BD55" s="18"/>
+      <c r="BE55" s="18"/>
+      <c r="BF55" s="18"/>
+      <c r="BG55" s="18"/>
+      <c r="BH55" s="18"/>
+      <c r="BI55" s="18"/>
+      <c r="BJ55" s="18"/>
+      <c r="BK55" s="18"/>
+      <c r="BL55" s="18"/>
+      <c r="BM55" s="18"/>
+      <c r="BN55" s="18"/>
+      <c r="BO55" s="18"/>
+      <c r="BP55" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="26">
     <mergeCell ref="AV26:BE26"/>
     <mergeCell ref="P14:Y14"/>
     <mergeCell ref="Z14:AL14"/>
+    <mergeCell ref="W12:BF12"/>
     <mergeCell ref="B42:K42"/>
     <mergeCell ref="L42:W42"/>
     <mergeCell ref="B32:I32"/>
@@ -2467,7 +2465,6 @@
     <mergeCell ref="B24:BO24"/>
     <mergeCell ref="B12:U12"/>
     <mergeCell ref="BG12:BQ12"/>
-    <mergeCell ref="V12:BF12"/>
     <mergeCell ref="B14:O14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates/request_equipment_template.xlsx
+++ b/templates/request_equipment_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CADFF5B1-4FB3-4857-B702-72E2F9AD4A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631259F1-ABA9-41AD-B822-C13B4D042F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4331DD6E-67AF-48F9-ABB9-6D96E0057117}"/>
   </bookViews>
@@ -220,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -282,9 +282,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -952,43 +949,43 @@
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
       <c r="U12" s="3"/>
-      <c r="V12" s="30"/>
-      <c r="W12" s="31"/>
-      <c r="X12" s="31"/>
-      <c r="Y12" s="31"/>
-      <c r="Z12" s="31"/>
-      <c r="AA12" s="31"/>
-      <c r="AB12" s="31"/>
-      <c r="AC12" s="31"/>
-      <c r="AD12" s="31"/>
-      <c r="AE12" s="31"/>
-      <c r="AF12" s="31"/>
-      <c r="AG12" s="31"/>
-      <c r="AH12" s="31"/>
-      <c r="AI12" s="31"/>
-      <c r="AJ12" s="31"/>
-      <c r="AK12" s="31"/>
-      <c r="AL12" s="31"/>
-      <c r="AM12" s="31"/>
-      <c r="AN12" s="31"/>
-      <c r="AO12" s="31"/>
-      <c r="AP12" s="31"/>
-      <c r="AQ12" s="31"/>
-      <c r="AR12" s="31"/>
-      <c r="AS12" s="31"/>
-      <c r="AT12" s="31"/>
-      <c r="AU12" s="31"/>
-      <c r="AV12" s="31"/>
-      <c r="AW12" s="31"/>
-      <c r="AX12" s="31"/>
-      <c r="AY12" s="31"/>
-      <c r="AZ12" s="31"/>
-      <c r="BA12" s="31"/>
-      <c r="BB12" s="31"/>
-      <c r="BC12" s="31"/>
-      <c r="BD12" s="31"/>
-      <c r="BE12" s="31"/>
-      <c r="BF12" s="31"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="30"/>
+      <c r="X12" s="30"/>
+      <c r="Y12" s="30"/>
+      <c r="Z12" s="30"/>
+      <c r="AA12" s="30"/>
+      <c r="AB12" s="30"/>
+      <c r="AC12" s="30"/>
+      <c r="AD12" s="30"/>
+      <c r="AE12" s="30"/>
+      <c r="AF12" s="30"/>
+      <c r="AG12" s="30"/>
+      <c r="AH12" s="30"/>
+      <c r="AI12" s="30"/>
+      <c r="AJ12" s="30"/>
+      <c r="AK12" s="30"/>
+      <c r="AL12" s="30"/>
+      <c r="AM12" s="30"/>
+      <c r="AN12" s="30"/>
+      <c r="AO12" s="30"/>
+      <c r="AP12" s="30"/>
+      <c r="AQ12" s="30"/>
+      <c r="AR12" s="30"/>
+      <c r="AS12" s="30"/>
+      <c r="AT12" s="30"/>
+      <c r="AU12" s="30"/>
+      <c r="AV12" s="30"/>
+      <c r="AW12" s="30"/>
+      <c r="AX12" s="30"/>
+      <c r="AY12" s="30"/>
+      <c r="AZ12" s="30"/>
+      <c r="BA12" s="30"/>
+      <c r="BB12" s="30"/>
+      <c r="BC12" s="30"/>
+      <c r="BD12" s="30"/>
+      <c r="BE12" s="30"/>
+      <c r="BF12" s="30"/>
       <c r="BG12" s="3" t="s">
         <v>1</v>
       </c>
@@ -1074,20 +1071,20 @@
       <c r="BQ13" s="5"/>
     </row>
     <row r="14" spans="2:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="31"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="31"/>
-      <c r="N14" s="31"/>
-      <c r="O14" s="31"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
       <c r="P14" s="2" t="s">
         <v>2</v>
       </c>
@@ -1100,19 +1097,19 @@
       <c r="W14" s="2"/>
       <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
-      <c r="Z14" s="31"/>
-      <c r="AA14" s="31"/>
-      <c r="AB14" s="31"/>
-      <c r="AC14" s="31"/>
-      <c r="AD14" s="31"/>
-      <c r="AE14" s="31"/>
-      <c r="AF14" s="31"/>
-      <c r="AG14" s="31"/>
-      <c r="AH14" s="31"/>
-      <c r="AI14" s="31"/>
-      <c r="AJ14" s="31"/>
-      <c r="AK14" s="31"/>
-      <c r="AL14" s="31"/>
+      <c r="Z14" s="30"/>
+      <c r="AA14" s="30"/>
+      <c r="AB14" s="30"/>
+      <c r="AC14" s="30"/>
+      <c r="AD14" s="30"/>
+      <c r="AE14" s="30"/>
+      <c r="AF14" s="30"/>
+      <c r="AG14" s="30"/>
+      <c r="AH14" s="30"/>
+      <c r="AI14" s="30"/>
+      <c r="AJ14" s="30"/>
+      <c r="AK14" s="30"/>
+      <c r="AL14" s="30"/>
       <c r="AM14" s="5" t="s">
         <v>3</v>
       </c>
@@ -1360,72 +1357,72 @@
       <c r="BQ17" s="6"/>
     </row>
     <row r="18" spans="2:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="32"/>
-      <c r="O18" s="32"/>
-      <c r="P18" s="32"/>
-      <c r="Q18" s="32"/>
-      <c r="R18" s="32"/>
-      <c r="S18" s="32"/>
-      <c r="T18" s="32"/>
-      <c r="U18" s="32"/>
-      <c r="V18" s="32"/>
-      <c r="W18" s="32"/>
-      <c r="X18" s="32"/>
-      <c r="Y18" s="32"/>
-      <c r="Z18" s="32"/>
-      <c r="AA18" s="32"/>
-      <c r="AB18" s="32"/>
-      <c r="AC18" s="32"/>
-      <c r="AD18" s="32"/>
-      <c r="AE18" s="32"/>
-      <c r="AF18" s="32"/>
-      <c r="AG18" s="32"/>
-      <c r="AH18" s="32"/>
-      <c r="AI18" s="32"/>
-      <c r="AJ18" s="32"/>
-      <c r="AK18" s="32"/>
-      <c r="AL18" s="32"/>
-      <c r="AM18" s="32"/>
-      <c r="AN18" s="32"/>
-      <c r="AO18" s="32"/>
-      <c r="AP18" s="32"/>
-      <c r="AQ18" s="32"/>
-      <c r="AR18" s="32"/>
-      <c r="AS18" s="32"/>
-      <c r="AT18" s="32"/>
-      <c r="AU18" s="32"/>
-      <c r="AV18" s="32"/>
-      <c r="AW18" s="32"/>
-      <c r="AX18" s="32"/>
-      <c r="AY18" s="32"/>
-      <c r="AZ18" s="32"/>
-      <c r="BA18" s="32"/>
-      <c r="BB18" s="32"/>
-      <c r="BC18" s="32"/>
-      <c r="BD18" s="32"/>
-      <c r="BE18" s="32"/>
-      <c r="BF18" s="32"/>
-      <c r="BG18" s="32"/>
-      <c r="BH18" s="32"/>
-      <c r="BI18" s="32"/>
-      <c r="BJ18" s="32"/>
-      <c r="BK18" s="32"/>
-      <c r="BL18" s="32"/>
-      <c r="BM18" s="32"/>
-      <c r="BN18" s="32"/>
-      <c r="BO18" s="32"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="31"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="31"/>
+      <c r="P18" s="31"/>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="31"/>
+      <c r="S18" s="31"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="31"/>
+      <c r="V18" s="31"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="31"/>
+      <c r="Z18" s="31"/>
+      <c r="AA18" s="31"/>
+      <c r="AB18" s="31"/>
+      <c r="AC18" s="31"/>
+      <c r="AD18" s="31"/>
+      <c r="AE18" s="31"/>
+      <c r="AF18" s="31"/>
+      <c r="AG18" s="31"/>
+      <c r="AH18" s="31"/>
+      <c r="AI18" s="31"/>
+      <c r="AJ18" s="31"/>
+      <c r="AK18" s="31"/>
+      <c r="AL18" s="31"/>
+      <c r="AM18" s="31"/>
+      <c r="AN18" s="31"/>
+      <c r="AO18" s="31"/>
+      <c r="AP18" s="31"/>
+      <c r="AQ18" s="31"/>
+      <c r="AR18" s="31"/>
+      <c r="AS18" s="31"/>
+      <c r="AT18" s="31"/>
+      <c r="AU18" s="31"/>
+      <c r="AV18" s="31"/>
+      <c r="AW18" s="31"/>
+      <c r="AX18" s="31"/>
+      <c r="AY18" s="31"/>
+      <c r="AZ18" s="31"/>
+      <c r="BA18" s="31"/>
+      <c r="BB18" s="31"/>
+      <c r="BC18" s="31"/>
+      <c r="BD18" s="31"/>
+      <c r="BE18" s="31"/>
+      <c r="BF18" s="31"/>
+      <c r="BG18" s="31"/>
+      <c r="BH18" s="31"/>
+      <c r="BI18" s="31"/>
+      <c r="BJ18" s="31"/>
+      <c r="BK18" s="31"/>
+      <c r="BL18" s="31"/>
+      <c r="BM18" s="31"/>
+      <c r="BN18" s="31"/>
+      <c r="BO18" s="31"/>
       <c r="BP18" s="29"/>
       <c r="BQ18" s="6"/>
     </row>
@@ -1500,72 +1497,72 @@
       <c r="BQ19" s="6"/>
     </row>
     <row r="20" spans="2:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
-      <c r="N20" s="32"/>
-      <c r="O20" s="32"/>
-      <c r="P20" s="32"/>
-      <c r="Q20" s="32"/>
-      <c r="R20" s="32"/>
-      <c r="S20" s="32"/>
-      <c r="T20" s="32"/>
-      <c r="U20" s="32"/>
-      <c r="V20" s="32"/>
-      <c r="W20" s="32"/>
-      <c r="X20" s="32"/>
-      <c r="Y20" s="32"/>
-      <c r="Z20" s="32"/>
-      <c r="AA20" s="32"/>
-      <c r="AB20" s="32"/>
-      <c r="AC20" s="32"/>
-      <c r="AD20" s="32"/>
-      <c r="AE20" s="32"/>
-      <c r="AF20" s="32"/>
-      <c r="AG20" s="32"/>
-      <c r="AH20" s="32"/>
-      <c r="AI20" s="32"/>
-      <c r="AJ20" s="32"/>
-      <c r="AK20" s="32"/>
-      <c r="AL20" s="32"/>
-      <c r="AM20" s="32"/>
-      <c r="AN20" s="32"/>
-      <c r="AO20" s="32"/>
-      <c r="AP20" s="32"/>
-      <c r="AQ20" s="32"/>
-      <c r="AR20" s="32"/>
-      <c r="AS20" s="32"/>
-      <c r="AT20" s="32"/>
-      <c r="AU20" s="32"/>
-      <c r="AV20" s="32"/>
-      <c r="AW20" s="32"/>
-      <c r="AX20" s="32"/>
-      <c r="AY20" s="32"/>
-      <c r="AZ20" s="32"/>
-      <c r="BA20" s="32"/>
-      <c r="BB20" s="32"/>
-      <c r="BC20" s="32"/>
-      <c r="BD20" s="32"/>
-      <c r="BE20" s="32"/>
-      <c r="BF20" s="32"/>
-      <c r="BG20" s="32"/>
-      <c r="BH20" s="32"/>
-      <c r="BI20" s="32"/>
-      <c r="BJ20" s="32"/>
-      <c r="BK20" s="32"/>
-      <c r="BL20" s="32"/>
-      <c r="BM20" s="32"/>
-      <c r="BN20" s="32"/>
-      <c r="BO20" s="32"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="31"/>
+      <c r="W20" s="31"/>
+      <c r="X20" s="31"/>
+      <c r="Y20" s="31"/>
+      <c r="Z20" s="31"/>
+      <c r="AA20" s="31"/>
+      <c r="AB20" s="31"/>
+      <c r="AC20" s="31"/>
+      <c r="AD20" s="31"/>
+      <c r="AE20" s="31"/>
+      <c r="AF20" s="31"/>
+      <c r="AG20" s="31"/>
+      <c r="AH20" s="31"/>
+      <c r="AI20" s="31"/>
+      <c r="AJ20" s="31"/>
+      <c r="AK20" s="31"/>
+      <c r="AL20" s="31"/>
+      <c r="AM20" s="31"/>
+      <c r="AN20" s="31"/>
+      <c r="AO20" s="31"/>
+      <c r="AP20" s="31"/>
+      <c r="AQ20" s="31"/>
+      <c r="AR20" s="31"/>
+      <c r="AS20" s="31"/>
+      <c r="AT20" s="31"/>
+      <c r="AU20" s="31"/>
+      <c r="AV20" s="31"/>
+      <c r="AW20" s="31"/>
+      <c r="AX20" s="31"/>
+      <c r="AY20" s="31"/>
+      <c r="AZ20" s="31"/>
+      <c r="BA20" s="31"/>
+      <c r="BB20" s="31"/>
+      <c r="BC20" s="31"/>
+      <c r="BD20" s="31"/>
+      <c r="BE20" s="31"/>
+      <c r="BF20" s="31"/>
+      <c r="BG20" s="31"/>
+      <c r="BH20" s="31"/>
+      <c r="BI20" s="31"/>
+      <c r="BJ20" s="31"/>
+      <c r="BK20" s="31"/>
+      <c r="BL20" s="31"/>
+      <c r="BM20" s="31"/>
+      <c r="BN20" s="31"/>
+      <c r="BO20" s="31"/>
       <c r="BP20" s="29"/>
       <c r="BQ20" s="6"/>
     </row>
@@ -1640,72 +1637,72 @@
       <c r="BQ21" s="1"/>
     </row>
     <row r="22" spans="2:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-      <c r="I22" s="32"/>
-      <c r="J22" s="32"/>
-      <c r="K22" s="32"/>
-      <c r="L22" s="32"/>
-      <c r="M22" s="32"/>
-      <c r="N22" s="32"/>
-      <c r="O22" s="32"/>
-      <c r="P22" s="32"/>
-      <c r="Q22" s="32"/>
-      <c r="R22" s="32"/>
-      <c r="S22" s="32"/>
-      <c r="T22" s="32"/>
-      <c r="U22" s="32"/>
-      <c r="V22" s="32"/>
-      <c r="W22" s="32"/>
-      <c r="X22" s="32"/>
-      <c r="Y22" s="32"/>
-      <c r="Z22" s="32"/>
-      <c r="AA22" s="32"/>
-      <c r="AB22" s="32"/>
-      <c r="AC22" s="32"/>
-      <c r="AD22" s="32"/>
-      <c r="AE22" s="32"/>
-      <c r="AF22" s="32"/>
-      <c r="AG22" s="32"/>
-      <c r="AH22" s="32"/>
-      <c r="AI22" s="32"/>
-      <c r="AJ22" s="32"/>
-      <c r="AK22" s="32"/>
-      <c r="AL22" s="32"/>
-      <c r="AM22" s="32"/>
-      <c r="AN22" s="32"/>
-      <c r="AO22" s="32"/>
-      <c r="AP22" s="32"/>
-      <c r="AQ22" s="32"/>
-      <c r="AR22" s="32"/>
-      <c r="AS22" s="32"/>
-      <c r="AT22" s="32"/>
-      <c r="AU22" s="32"/>
-      <c r="AV22" s="32"/>
-      <c r="AW22" s="32"/>
-      <c r="AX22" s="32"/>
-      <c r="AY22" s="32"/>
-      <c r="AZ22" s="32"/>
-      <c r="BA22" s="32"/>
-      <c r="BB22" s="32"/>
-      <c r="BC22" s="32"/>
-      <c r="BD22" s="32"/>
-      <c r="BE22" s="32"/>
-      <c r="BF22" s="32"/>
-      <c r="BG22" s="32"/>
-      <c r="BH22" s="32"/>
-      <c r="BI22" s="32"/>
-      <c r="BJ22" s="32"/>
-      <c r="BK22" s="32"/>
-      <c r="BL22" s="32"/>
-      <c r="BM22" s="32"/>
-      <c r="BN22" s="32"/>
-      <c r="BO22" s="32"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="31"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="31"/>
+      <c r="P22" s="31"/>
+      <c r="Q22" s="31"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="31"/>
+      <c r="V22" s="31"/>
+      <c r="W22" s="31"/>
+      <c r="X22" s="31"/>
+      <c r="Y22" s="31"/>
+      <c r="Z22" s="31"/>
+      <c r="AA22" s="31"/>
+      <c r="AB22" s="31"/>
+      <c r="AC22" s="31"/>
+      <c r="AD22" s="31"/>
+      <c r="AE22" s="31"/>
+      <c r="AF22" s="31"/>
+      <c r="AG22" s="31"/>
+      <c r="AH22" s="31"/>
+      <c r="AI22" s="31"/>
+      <c r="AJ22" s="31"/>
+      <c r="AK22" s="31"/>
+      <c r="AL22" s="31"/>
+      <c r="AM22" s="31"/>
+      <c r="AN22" s="31"/>
+      <c r="AO22" s="31"/>
+      <c r="AP22" s="31"/>
+      <c r="AQ22" s="31"/>
+      <c r="AR22" s="31"/>
+      <c r="AS22" s="31"/>
+      <c r="AT22" s="31"/>
+      <c r="AU22" s="31"/>
+      <c r="AV22" s="31"/>
+      <c r="AW22" s="31"/>
+      <c r="AX22" s="31"/>
+      <c r="AY22" s="31"/>
+      <c r="AZ22" s="31"/>
+      <c r="BA22" s="31"/>
+      <c r="BB22" s="31"/>
+      <c r="BC22" s="31"/>
+      <c r="BD22" s="31"/>
+      <c r="BE22" s="31"/>
+      <c r="BF22" s="31"/>
+      <c r="BG22" s="31"/>
+      <c r="BH22" s="31"/>
+      <c r="BI22" s="31"/>
+      <c r="BJ22" s="31"/>
+      <c r="BK22" s="31"/>
+      <c r="BL22" s="31"/>
+      <c r="BM22" s="31"/>
+      <c r="BN22" s="31"/>
+      <c r="BO22" s="31"/>
       <c r="BP22" s="29"/>
       <c r="BQ22" s="1"/>
     </row>
@@ -1780,72 +1777,72 @@
       <c r="BQ23" s="1"/>
     </row>
     <row r="24" spans="2:69" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="32"/>
-      <c r="I24" s="32"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="32"/>
-      <c r="L24" s="32"/>
-      <c r="M24" s="32"/>
-      <c r="N24" s="32"/>
-      <c r="O24" s="32"/>
-      <c r="P24" s="32"/>
-      <c r="Q24" s="32"/>
-      <c r="R24" s="32"/>
-      <c r="S24" s="32"/>
-      <c r="T24" s="32"/>
-      <c r="U24" s="32"/>
-      <c r="V24" s="32"/>
-      <c r="W24" s="32"/>
-      <c r="X24" s="32"/>
-      <c r="Y24" s="32"/>
-      <c r="Z24" s="32"/>
-      <c r="AA24" s="32"/>
-      <c r="AB24" s="32"/>
-      <c r="AC24" s="32"/>
-      <c r="AD24" s="32"/>
-      <c r="AE24" s="32"/>
-      <c r="AF24" s="32"/>
-      <c r="AG24" s="32"/>
-      <c r="AH24" s="32"/>
-      <c r="AI24" s="32"/>
-      <c r="AJ24" s="32"/>
-      <c r="AK24" s="32"/>
-      <c r="AL24" s="32"/>
-      <c r="AM24" s="32"/>
-      <c r="AN24" s="32"/>
-      <c r="AO24" s="32"/>
-      <c r="AP24" s="32"/>
-      <c r="AQ24" s="32"/>
-      <c r="AR24" s="32"/>
-      <c r="AS24" s="32"/>
-      <c r="AT24" s="32"/>
-      <c r="AU24" s="32"/>
-      <c r="AV24" s="32"/>
-      <c r="AW24" s="32"/>
-      <c r="AX24" s="32"/>
-      <c r="AY24" s="32"/>
-      <c r="AZ24" s="32"/>
-      <c r="BA24" s="32"/>
-      <c r="BB24" s="32"/>
-      <c r="BC24" s="32"/>
-      <c r="BD24" s="32"/>
-      <c r="BE24" s="32"/>
-      <c r="BF24" s="32"/>
-      <c r="BG24" s="32"/>
-      <c r="BH24" s="32"/>
-      <c r="BI24" s="32"/>
-      <c r="BJ24" s="32"/>
-      <c r="BK24" s="32"/>
-      <c r="BL24" s="32"/>
-      <c r="BM24" s="32"/>
-      <c r="BN24" s="32"/>
-      <c r="BO24" s="32"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="31"/>
+      <c r="N24" s="31"/>
+      <c r="O24" s="31"/>
+      <c r="P24" s="31"/>
+      <c r="Q24" s="31"/>
+      <c r="R24" s="31"/>
+      <c r="S24" s="31"/>
+      <c r="T24" s="31"/>
+      <c r="U24" s="31"/>
+      <c r="V24" s="31"/>
+      <c r="W24" s="31"/>
+      <c r="X24" s="31"/>
+      <c r="Y24" s="31"/>
+      <c r="Z24" s="31"/>
+      <c r="AA24" s="31"/>
+      <c r="AB24" s="31"/>
+      <c r="AC24" s="31"/>
+      <c r="AD24" s="31"/>
+      <c r="AE24" s="31"/>
+      <c r="AF24" s="31"/>
+      <c r="AG24" s="31"/>
+      <c r="AH24" s="31"/>
+      <c r="AI24" s="31"/>
+      <c r="AJ24" s="31"/>
+      <c r="AK24" s="31"/>
+      <c r="AL24" s="31"/>
+      <c r="AM24" s="31"/>
+      <c r="AN24" s="31"/>
+      <c r="AO24" s="31"/>
+      <c r="AP24" s="31"/>
+      <c r="AQ24" s="31"/>
+      <c r="AR24" s="31"/>
+      <c r="AS24" s="31"/>
+      <c r="AT24" s="31"/>
+      <c r="AU24" s="31"/>
+      <c r="AV24" s="31"/>
+      <c r="AW24" s="31"/>
+      <c r="AX24" s="31"/>
+      <c r="AY24" s="31"/>
+      <c r="AZ24" s="31"/>
+      <c r="BA24" s="31"/>
+      <c r="BB24" s="31"/>
+      <c r="BC24" s="31"/>
+      <c r="BD24" s="31"/>
+      <c r="BE24" s="31"/>
+      <c r="BF24" s="31"/>
+      <c r="BG24" s="31"/>
+      <c r="BH24" s="31"/>
+      <c r="BI24" s="31"/>
+      <c r="BJ24" s="31"/>
+      <c r="BK24" s="31"/>
+      <c r="BL24" s="31"/>
+      <c r="BM24" s="31"/>
+      <c r="BN24" s="31"/>
+      <c r="BO24" s="31"/>
       <c r="BP24" s="29"/>
     </row>
     <row r="25" spans="2:69" ht="2.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1857,34 +1854,34 @@
       <c r="G25" s="1"/>
     </row>
     <row r="26" spans="2:69" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
+      <c r="B26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="31"/>
-      <c r="W26" s="31"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="31"/>
-      <c r="Z26" s="31"/>
-      <c r="AA26" s="31"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
+      <c r="AA26" s="30"/>
       <c r="AB26" s="21"/>
       <c r="AC26" s="2" t="s">
         <v>5</v>
@@ -1907,16 +1904,16 @@
       <c r="AS26" s="2"/>
       <c r="AT26" s="2"/>
       <c r="AU26" s="2"/>
-      <c r="AV26" s="31"/>
-      <c r="AW26" s="31"/>
-      <c r="AX26" s="31"/>
-      <c r="AY26" s="31"/>
-      <c r="AZ26" s="31"/>
-      <c r="BA26" s="31"/>
-      <c r="BB26" s="31"/>
-      <c r="BC26" s="31"/>
-      <c r="BD26" s="31"/>
-      <c r="BE26" s="31"/>
+      <c r="AV26" s="30"/>
+      <c r="AW26" s="30"/>
+      <c r="AX26" s="30"/>
+      <c r="AY26" s="30"/>
+      <c r="AZ26" s="30"/>
+      <c r="BA26" s="30"/>
+      <c r="BB26" s="30"/>
+      <c r="BC26" s="30"/>
+      <c r="BD26" s="30"/>
+      <c r="BE26" s="30"/>
       <c r="BF26" s="21"/>
       <c r="BG26" s="21"/>
       <c r="BH26" s="21"/>
@@ -1973,18 +1970,18 @@
       <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="31"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="31"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
     </row>
     <row r="33" spans="2:56" x14ac:dyDescent="0.25">
       <c r="B33" s="1"/>
@@ -2146,18 +2143,18 @@
       <c r="I42" s="3"/>
       <c r="J42" s="3"/>
       <c r="K42" s="3"/>
-      <c r="L42" s="31"/>
-      <c r="M42" s="31"/>
-      <c r="N42" s="31"/>
-      <c r="O42" s="31"/>
-      <c r="P42" s="31"/>
-      <c r="Q42" s="31"/>
-      <c r="R42" s="31"/>
-      <c r="S42" s="31"/>
-      <c r="T42" s="31"/>
-      <c r="U42" s="31"/>
-      <c r="V42" s="31"/>
-      <c r="W42" s="31"/>
+      <c r="L42" s="30"/>
+      <c r="M42" s="30"/>
+      <c r="N42" s="30"/>
+      <c r="O42" s="30"/>
+      <c r="P42" s="30"/>
+      <c r="Q42" s="30"/>
+      <c r="R42" s="30"/>
+      <c r="S42" s="30"/>
+      <c r="T42" s="30"/>
+      <c r="U42" s="30"/>
+      <c r="V42" s="30"/>
+      <c r="W42" s="30"/>
     </row>
     <row r="44" spans="2:56" x14ac:dyDescent="0.25">
       <c r="M44" s="13" t="s">
@@ -2444,11 +2441,12 @@
     <mergeCell ref="P14:Y14"/>
     <mergeCell ref="Z14:AL14"/>
     <mergeCell ref="W12:BF12"/>
+    <mergeCell ref="B12:V12"/>
+    <mergeCell ref="B26:P26"/>
     <mergeCell ref="B42:K42"/>
     <mergeCell ref="L42:W42"/>
     <mergeCell ref="B32:I32"/>
     <mergeCell ref="J32:U32"/>
-    <mergeCell ref="B26:O26"/>
     <mergeCell ref="Q26:AA26"/>
     <mergeCell ref="AC26:AU26"/>
     <mergeCell ref="B8:BO9"/>
@@ -2463,7 +2461,6 @@
     <mergeCell ref="B20:BO20"/>
     <mergeCell ref="B22:BO22"/>
     <mergeCell ref="B24:BO24"/>
-    <mergeCell ref="B12:U12"/>
     <mergeCell ref="BG12:BQ12"/>
     <mergeCell ref="B14:O14"/>
   </mergeCells>

--- a/templates/request_equipment_template.xlsx
+++ b/templates/request_equipment_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631259F1-ABA9-41AD-B822-C13B4D042F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F523761-301C-4712-9A4D-D23EFE1ABECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{4331DD6E-67AF-48F9-ABB9-6D96E0057117}"/>
   </bookViews>
@@ -311,15 +311,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>5955</xdr:colOff>
+      <xdr:colOff>5954</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>5953</xdr:rowOff>
+      <xdr:rowOff>5952</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>28181</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>36005</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>82453</xdr:rowOff>
+      <xdr:rowOff>171449</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -348,8 +348,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="101205" y="196453"/>
-          <a:ext cx="2593976" cy="648000"/>
+          <a:off x="94854" y="196452"/>
+          <a:ext cx="2874851" cy="736997"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
